--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O196"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,36 +496,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
+          <t>7c927eef9664b42ce0e8b22e4c434a06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>minerva.aidevhost.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-03-08T15:21:59.158817Z</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-03-08T15:21:59.158817Z</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
+          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -600,12 +600,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2026-02-23T09:20:55.788713Z</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2026-02-23T09:20:55.788713Z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
+          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -659,12 +659,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:15.423313Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:54.530581Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>66de4cd56c98d8faddaffb325bc296bd</t>
+          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -718,12 +718,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.147955Z</t>
+          <t>2025-12-27T19:42:15.423313Z</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:53.92293Z</t>
+          <t>2026-02-23T09:20:54.530581Z</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -732,12 +732,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2b8843986f866d3e99f4d6834382282e</t>
+          <t>66de4cd56c98d8faddaffb325bc296bd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>www.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -777,12 +777,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2025-12-27T19:42:16.147955Z</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2026-02-23T09:20:53.92293Z</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a7884955fee4043702153da01228b09f</t>
+          <t>2b8843986f866d3e99f4d6834382282e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -836,12 +836,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.950308Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.922031Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -850,7 +850,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
+          <t>a7884955fee4043702153da01228b09f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -895,12 +895,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:17.693642Z</t>
+          <t>2025-12-27T19:42:16.950308Z</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.313669Z</t>
+          <t>2026-02-23T09:21:07.922031Z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -909,7 +909,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>401726adb31f75b18399e2039d73d307</t>
+          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -954,12 +954,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:18.539481Z</t>
+          <t>2025-12-27T19:42:17.693642Z</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:06.591532Z</t>
+          <t>2026-02-23T09:21:07.313669Z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -968,32 +968,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
+          <t>401726adb31f75b18399e2039d73d307</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>www.audiolibri.org</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1013,25 +1013,21 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
+          <t>2025-12-27T19:42:18.539481Z</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-02-23T09:21:06.591532Z</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
+          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1046,7 +1042,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -1076,17 +1072,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1094,7 +1090,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c4b015ebb6540fa1c64482131c937ad9</t>
+          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1104,12 +1100,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1139,26 +1135,30 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:26.735522Z</t>
+          <t>2026-02-23T09:20:58.143923Z</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:57.512009Z</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>2026-02-23T09:20:58.143923Z</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8123b69792536eda89581575fc5e6501</t>
+          <t>c4b015ebb6540fa1c64482131c937ad9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>_dmarc.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:38.385312Z</t>
+          <t>2022-01-24T18:09:26.735522Z</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:01.139092Z</t>
+          <t>2026-02-23T09:20:57.512009Z</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1212,32 +1212,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
+          <t>8123b69792536eda89581575fc5e6501</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>www.certmate.org</t>
+          <t>_dmarc.audiolibri.org</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>185.199.109.153</t>
+          <t>v=DMARC1; p=reject</t>
         </is>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2025-07-01T16:44:05.723652Z</t>
+          <t>2022-01-24T18:09:38.385312Z</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2025-07-01T16:47:41.146282Z</t>
+          <t>2026-02-23T09:21:01.139092Z</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1271,29 +1271,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9a0c1ea7682256e45af5f83341fb113e</t>
+          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>www.certmate.org</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>185.199.109.153</t>
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1316,23 +1316,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:44:05.723652Z</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:47:41.146282Z</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>34</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aecf0cef3bc28aa58695c24be19d992c</t>
+          <t>9a0c1ea7682256e45af5f83341fb113e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1347,7 +1345,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1377,23 +1375,23 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fd67f08c9417a7d074fabd7e5513f715</t>
+          <t>aecf0cef3bc28aa58695c24be19d992c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1408,7 +1406,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1438,38 +1436,38 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14ecb7082a212233d816e345eea11668</t>
+          <t>fd67f08c9417a7d074fabd7e5513f715</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>test.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ns-858.awsdns-43.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1488,7 +1486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1499,21 +1497,23 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0b4d1e1437d207800341e642f54e492f</t>
+          <t>14ecb7082a212233d816e345eea11668</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ns-8.awsdns-01.com</t>
+          <t>ns-858.awsdns-43.net</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
+          <t>0b4d1e1437d207800341e642f54e492f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ns-1790.awsdns-31.co.uk</t>
+          <t>ns-8.awsdns-01.com</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>759120960fb1797f3ceb20a074397a60</t>
+          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ns-1479.awsdns-56.org</t>
+          <t>ns-1790.awsdns-31.co.uk</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1690,22 +1690,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>abd1e138555a9935af96e12e735ae62e</t>
+          <t>759120960fb1797f3ceb20a074397a60</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>test.certmate.org</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>ns-1479.awsdns-56.org</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1749,12 +1749,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
+          <t>abd1e138555a9935af96e12e735ae62e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1808,41 +1808,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>cf2024-1._domainkey.certmate.org</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1867,12 +1867,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1926,12 +1926,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -1985,12 +1985,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2044,12 +2044,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2177,14 +2177,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2236,14 +2236,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2280,26 +2280,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -2325,23 +2325,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>80</v>
-      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2356,7 +2354,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -2386,23 +2384,23 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2417,7 +2415,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -2447,38 +2445,38 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -2508,26 +2506,28 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2581,12 +2581,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2640,32 +2640,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2758,12 +2758,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2876,7 +2876,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2994,12 +2994,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3053,7 +3053,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3230,12 +3230,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3304,11 +3304,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3348,12 +3348,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3407,12 +3407,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3584,12 +3584,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3702,12 +3702,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3761,12 +3761,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3997,12 +3997,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4115,12 +4115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4174,12 +4174,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4292,12 +4292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4410,12 +4410,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4528,12 +4528,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4587,12 +4587,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4705,12 +4705,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4764,12 +4764,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5059,22 +5059,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5104,25 +5104,21 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-01-17T09:16:10.204614Z</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5137,7 +5133,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5167,17 +5163,17 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
@@ -5185,26 +5181,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -5214,7 +5210,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5230,26 +5226,30 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>2025-12-26T23:53:31.459246Z</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5303,12 +5303,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5362,12 +5362,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5421,12 +5421,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5480,12 +5480,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5539,12 +5539,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5598,26 +5598,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5657,12 +5657,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5716,32 +5716,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5775,12 +5775,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5834,12 +5834,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -5893,12 +5893,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -5952,22 +5952,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6011,36 +6011,36 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6056,38 +6056,36 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>10</v>
-      </c>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -6117,26 +6115,28 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6249,12 +6249,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6308,36 +6308,36 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6426,12 +6426,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6485,36 +6485,36 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6544,12 +6544,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -6569,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>3600</v>
+        <v>120</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6603,22 +6603,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -6628,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6662,22 +6662,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6707,12 +6707,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6721,36 +6721,36 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -6780,12 +6780,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6839,12 +6839,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -6898,12 +6898,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -6957,12 +6957,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7016,12 +7016,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7075,12 +7075,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7134,12 +7134,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7193,12 +7193,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7252,12 +7252,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7311,12 +7311,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7370,12 +7370,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7429,12 +7429,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7488,12 +7488,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
         <v>1</v>
       </c>
       <c r="F120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7547,12 +7547,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7606,12 +7606,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E122" t="b">
         <v>1</v>
       </c>
       <c r="F122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7665,12 +7665,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7724,12 +7724,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7783,12 +7783,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7842,12 +7842,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -7887,12 +7887,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7901,12 +7901,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7960,12 +7960,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8019,12 +8019,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8034,14 +8034,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E129" t="b">
         <v>1</v>
       </c>
       <c r="F129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8078,12 +8078,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8137,12 +8137,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8152,14 +8152,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E131" t="b">
         <v>1</v>
       </c>
       <c r="F131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -8182,12 +8182,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8196,12 +8196,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8255,12 +8255,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8314,12 +8314,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8373,12 +8373,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8432,36 +8432,36 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8477,23 +8477,21 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
-      <c r="O136" t="n">
-        <v>1</v>
-      </c>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8508,7 +8506,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8538,23 +8536,23 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8569,7 +8567,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8599,23 +8597,23 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8630,7 +8628,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8660,38 +8658,38 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8721,36 +8719,38 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -8760,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8794,12 +8794,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -8819,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -8971,12 +8971,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9030,7 +9030,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9075,12 +9075,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9148,7 +9148,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9207,12 +9207,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9266,12 +9266,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9325,12 +9325,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9384,22 +9384,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9409,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9429,12 +9429,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9443,36 +9443,36 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9502,12 +9502,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9561,12 +9561,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9620,12 +9620,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9679,12 +9679,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9738,12 +9738,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9797,36 +9797,36 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -9856,22 +9856,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -9915,7 +9915,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -9974,22 +9974,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10092,7 +10092,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10151,36 +10151,36 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10210,12 +10210,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10269,36 +10269,36 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E167" t="b">
         <v>1</v>
       </c>
       <c r="F167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10328,12 +10328,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10387,12 +10387,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10446,12 +10446,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10468,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="F170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -10491,12 +10491,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10505,22 +10505,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10564,12 +10564,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10609,12 +10609,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10623,12 +10623,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10668,12 +10668,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10682,12 +10682,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10741,12 +10741,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10800,12 +10800,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10859,12 +10859,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10918,41 +10918,41 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
@@ -10963,23 +10963,21 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" t="n">
-        <v>40</v>
-      </c>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10994,7 +10992,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -11024,23 +11022,23 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11055,7 +11053,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -11085,38 +11083,38 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11146,26 +11144,28 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
+      <c r="O181" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,12 +11219,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11337,7 +11337,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11396,12 +11396,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11455,12 +11455,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,12 +11514,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,12 +11573,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -11618,12 +11618,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11632,12 +11632,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11691,12 +11691,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11750,29 +11750,29 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11809,12 +11809,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11868,12 +11868,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11927,12 +11927,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11986,22 +11986,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12031,16 +12031,75 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E197" t="b">
+        <v>1</v>
+      </c>
+      <c r="F197" t="b">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O197"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6721,22 +6721,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -6766,55 +6766,57 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -6825,55 +6827,57 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -6884,50 +6888,52 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6943,12 +6949,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -6957,41 +6963,41 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -7002,12 +7008,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7016,36 +7022,36 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7061,12 +7067,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7075,12 +7081,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7090,7 +7096,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -7120,12 +7126,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7134,12 +7140,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7179,12 +7185,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7193,12 +7199,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7208,7 +7214,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7238,12 +7244,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7252,12 +7258,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7267,7 +7273,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7297,12 +7303,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7311,12 +7317,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7326,7 +7332,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7356,12 +7362,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7370,12 +7376,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7385,7 +7391,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7415,12 +7421,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7429,12 +7435,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7444,7 +7450,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7474,12 +7480,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7488,12 +7494,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7503,7 +7509,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -7533,12 +7539,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7547,12 +7553,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7562,14 +7568,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E121" t="b">
         <v>1</v>
       </c>
       <c r="F121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -7592,12 +7598,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7606,12 +7612,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7621,14 +7627,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E122" t="b">
         <v>1</v>
       </c>
       <c r="F122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -7651,12 +7657,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7665,12 +7671,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7680,7 +7686,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7710,12 +7716,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7724,12 +7730,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7739,7 +7745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7769,12 +7775,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7783,12 +7789,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7798,7 +7804,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7828,12 +7834,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7842,12 +7848,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7857,14 +7863,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E126" t="b">
         <v>1</v>
       </c>
       <c r="F126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -7887,12 +7893,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7901,12 +7907,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7916,14 +7922,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E127" t="b">
         <v>1</v>
       </c>
       <c r="F127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -7946,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7960,12 +7966,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7975,7 +7981,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8005,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8019,12 +8025,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8034,7 +8040,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8064,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8078,12 +8084,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8093,14 +8099,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E130" t="b">
         <v>1</v>
       </c>
       <c r="F130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -8123,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8137,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8152,14 +8158,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E131" t="b">
         <v>1</v>
       </c>
       <c r="F131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -8182,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8196,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8211,7 +8217,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8241,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8255,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8270,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8300,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8314,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8329,7 +8335,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8359,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8373,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8388,14 +8394,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E135" t="b">
         <v>1</v>
       </c>
       <c r="F135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -8418,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8432,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8447,14 +8453,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E136" t="b">
         <v>1</v>
       </c>
       <c r="F136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -8477,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8491,36 +8497,36 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8536,52 +8542,50 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="n">
-        <v>1</v>
-      </c>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8597,52 +8601,50 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="n">
-        <v>73</v>
-      </c>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8658,52 +8660,50 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
-      <c r="O139" t="n">
-        <v>99</v>
-      </c>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8719,52 +8719,50 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="n">
-        <v>89</v>
-      </c>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8780,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8794,22 +8792,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -8819,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -8839,36 +8837,38 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -8898,36 +8898,38 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+      <c r="O143" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -8957,36 +8959,38 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
+      <c r="O144" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9016,36 +9020,38 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9075,12 +9081,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9089,12 +9095,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9104,7 +9110,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9114,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9134,12 +9140,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9148,12 +9154,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9163,7 +9169,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9193,12 +9199,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9207,12 +9213,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9222,7 +9228,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9252,12 +9258,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9266,12 +9272,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9281,7 +9287,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9311,12 +9317,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9325,12 +9331,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9340,7 +9346,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9370,12 +9376,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9384,12 +9390,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9399,7 +9405,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9429,12 +9435,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9443,22 +9449,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9468,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9488,12 +9494,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9502,36 +9508,36 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9547,12 +9553,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9561,36 +9567,36 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9606,12 +9612,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9620,36 +9626,36 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9665,12 +9671,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9679,36 +9685,36 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9724,12 +9730,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9738,36 +9744,36 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9783,12 +9789,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9797,12 +9803,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9812,7 +9818,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -9842,12 +9848,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -9856,36 +9862,36 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9901,12 +9907,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -9915,36 +9921,36 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
         <v>1</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9960,12 +9966,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -9974,36 +9980,36 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10019,12 +10025,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10033,36 +10039,36 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10078,12 +10084,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10092,36 +10098,36 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
         <v>1</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10137,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10151,12 +10157,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10166,7 +10172,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10176,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -10196,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10210,36 +10216,36 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10255,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10269,36 +10275,36 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10314,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10328,26 +10334,26 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168" t="b">
         <v>0</v>
@@ -10373,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10387,26 +10393,26 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" t="b">
         <v>0</v>
@@ -10432,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10446,26 +10452,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170" t="b">
         <v>0</v>
@@ -10491,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10505,22 +10511,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10534,7 +10540,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10550,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10564,12 +10570,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10579,7 +10585,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10609,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10623,36 +10629,36 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E173" t="b">
         <v>1</v>
       </c>
       <c r="F173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>1</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10668,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10682,36 +10688,36 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E174" t="b">
         <v>1</v>
       </c>
       <c r="F174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10727,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10741,36 +10747,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E175" t="b">
         <v>1</v>
       </c>
       <c r="F175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10786,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10800,22 +10806,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -10829,7 +10835,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10845,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10859,12 +10865,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10874,7 +10880,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -10904,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10918,12 +10924,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10933,7 +10939,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -10963,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10977,41 +10983,41 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
@@ -11022,23 +11028,21 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
-      <c r="O179" t="n">
-        <v>40</v>
-      </c>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11048,31 +11052,31 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
         <v>1</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
@@ -11083,57 +11087,55 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
-      <c r="O180" t="n">
-        <v>90</v>
-      </c>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
@@ -11144,57 +11146,55 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
-      <c r="O181" t="n">
-        <v>97</v>
-      </c>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,36 +11219,36 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -11323,21 +11323,23 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11347,12 +11349,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11371,7 +11373,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -11382,21 +11384,23 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
+      <c r="O185" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11406,12 +11410,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -11430,7 +11434,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -11441,26 +11445,28 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
+      <c r="O186" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11470,7 +11476,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11489,7 +11495,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -11500,12 +11506,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,12 +11520,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11529,7 +11535,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11559,12 +11565,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,12 +11579,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11588,7 +11594,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11607,7 +11613,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -11618,12 +11624,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11632,12 +11638,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11647,7 +11653,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11677,12 +11683,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11691,12 +11697,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11706,7 +11712,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11736,12 +11742,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11750,12 +11756,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11765,7 +11771,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -11795,12 +11801,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11809,29 +11815,29 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -11854,12 +11860,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11868,29 +11874,29 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
@@ -11902,7 +11908,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -11913,12 +11919,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11927,29 +11933,29 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>1</v>
@@ -11972,12 +11978,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11986,29 +11992,29 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -12031,12 +12037,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12045,36 +12051,36 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
         <v>1</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12090,16 +12096,311 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E198" t="b">
+        <v>1</v>
+      </c>
+      <c r="F198" t="b">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2023-03-30T09:59:11.98058Z</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2023-03-30T09:59:12.228482Z</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>test2.webtek.live</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E199" t="b">
+        <v>1</v>
+      </c>
+      <c r="F199" t="b">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:29.902515Z</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:30.164318Z</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>432df2553b443742f9f905e155878536</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>test.webtek.live</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E200" t="b">
+        <v>1</v>
+      </c>
+      <c r="F200" t="b">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.078812Z</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.367412Z</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>webtek.live</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E201" t="b">
+        <v>1</v>
+      </c>
+      <c r="F201" t="b">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E202" t="b">
+        <v>1</v>
+      </c>
+      <c r="F202" t="b">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O202"/>
+  <dimension ref="A1:O206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6721,22 +6721,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -6766,38 +6766,36 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="n">
-        <v>58</v>
-      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -6816,7 +6814,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -6827,38 +6825,36 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="n">
-        <v>66</v>
-      </c>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6877,7 +6873,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -6888,38 +6884,36 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="n">
-        <v>84</v>
-      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6929,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -6938,7 +6932,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -6949,36 +6943,38 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -7008,21 +7004,23 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7032,12 +7030,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7056,7 +7054,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -7067,50 +7065,52 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7140,41 +7140,41 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7199,36 +7199,36 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7258,36 +7258,36 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7317,12 +7317,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7376,12 +7376,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7435,12 +7435,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7494,12 +7494,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7553,12 +7553,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7612,12 +7612,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7671,12 +7671,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7730,12 +7730,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7848,12 +7848,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7863,14 +7863,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E126" t="b">
         <v>1</v>
       </c>
       <c r="F126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7907,12 +7907,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E127" t="b">
         <v>1</v>
       </c>
       <c r="F127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -7952,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7966,12 +7966,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8099,14 +8099,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E130" t="b">
         <v>1</v>
       </c>
       <c r="F130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8158,14 +8158,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E131" t="b">
         <v>1</v>
       </c>
       <c r="F131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8261,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8379,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8394,14 +8394,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
         <v>1</v>
       </c>
       <c r="F135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -8424,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8453,14 +8453,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
         <v>1</v>
       </c>
       <c r="F136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8556,12 +8556,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8630,14 +8630,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E139" t="b">
         <v>1</v>
       </c>
       <c r="F139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E140" t="b">
         <v>1</v>
       </c>
       <c r="F140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8792,36 +8792,36 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8837,52 +8837,50 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="n">
-        <v>1</v>
-      </c>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8898,52 +8896,50 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="n">
-        <v>73</v>
-      </c>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8959,52 +8955,50 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="n">
-        <v>99</v>
-      </c>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9020,38 +9014,36 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="n">
-        <v>89</v>
-      </c>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9081,36 +9073,38 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9120,7 +9114,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9140,36 +9134,38 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="O147" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9199,36 +9195,38 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
+      <c r="O148" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9258,36 +9256,38 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9356,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9390,12 +9390,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9449,12 +9449,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9508,12 +9508,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9567,12 +9567,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9626,12 +9626,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9685,12 +9685,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9744,22 +9744,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -9789,12 +9789,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9803,36 +9803,36 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
         <v>1</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -9862,36 +9862,36 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -9921,36 +9921,36 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
         <v>1</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -9980,36 +9980,36 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10039,12 +10039,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10098,12 +10098,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10157,36 +10157,36 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10216,36 +10216,36 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10275,36 +10275,36 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10334,36 +10334,36 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10393,12 +10393,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -10418,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10452,22 +10452,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10511,36 +10511,36 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10570,36 +10570,36 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10629,26 +10629,26 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="b">
         <v>0</v>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10688,26 +10688,26 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" t="b">
         <v>0</v>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10747,36 +10747,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E175" t="b">
         <v>1</v>
       </c>
       <c r="F175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10806,22 +10806,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10865,36 +10865,36 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E177" t="b">
         <v>1</v>
       </c>
       <c r="F177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10924,36 +10924,36 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E178" t="b">
         <v>1</v>
       </c>
       <c r="F178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10983,36 +10983,36 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E179" t="b">
         <v>1</v>
       </c>
       <c r="F179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11042,22 +11042,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11101,12 +11101,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11160,12 +11160,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,12 +11219,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11288,31 +11288,31 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -11323,57 +11323,55 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="n">
-        <v>40</v>
-      </c>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -11384,57 +11382,55 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="n">
-        <v>90</v>
-      </c>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -11445,57 +11441,55 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
-      <c r="O186" t="n">
-        <v>97</v>
-      </c>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
         <v>1</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -11506,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11520,22 +11514,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11554,7 +11548,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -11565,21 +11559,23 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
+      <c r="O188" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11589,12 +11585,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11613,7 +11609,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -11624,21 +11620,23 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11648,12 +11646,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11672,7 +11670,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -11683,26 +11681,28 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="O190" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -11742,12 +11742,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11756,12 +11756,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11815,12 +11815,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -11860,12 +11860,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11874,12 +11874,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11933,12 +11933,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11992,12 +11992,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12051,12 +12051,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12110,29 +12110,29 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -12155,12 +12155,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12169,29 +12169,29 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -12214,12 +12214,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12228,29 +12228,29 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
         <v>1</v>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12287,29 +12287,29 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
         <v>1</v>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -12346,22 +12346,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12391,16 +12391,252 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>test2.webtek.live</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E203" t="b">
+        <v>1</v>
+      </c>
+      <c r="F203" t="b">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:29.902515Z</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:30.164318Z</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>432df2553b443742f9f905e155878536</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>test.webtek.live</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E204" t="b">
+        <v>1</v>
+      </c>
+      <c r="F204" t="b">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.078812Z</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.367412Z</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>webtek.live</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E205" t="b">
+        <v>1</v>
+      </c>
+      <c r="F205" t="b">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E206" t="b">
+        <v>1</v>
+      </c>
+      <c r="F206" t="b">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O206"/>
+  <dimension ref="A1:O207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,12 +2280,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2295,14 +2295,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2339,26 +2339,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -2384,23 +2384,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>80</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2415,7 +2413,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -2445,23 +2443,23 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2476,7 +2474,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -2506,38 +2504,38 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -2567,26 +2565,28 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2640,12 +2640,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2699,32 +2699,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2758,12 +2758,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2817,12 +2817,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2876,7 +2876,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3053,12 +3053,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3348,12 +3348,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3407,12 +3407,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3584,12 +3584,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3643,12 +3643,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3761,12 +3761,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3820,12 +3820,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3997,7 +3997,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4071,17 +4071,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4115,12 +4115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4174,12 +4174,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4292,12 +4292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4376,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4410,12 +4410,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4528,12 +4528,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4587,12 +4587,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4705,12 +4705,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4764,12 +4764,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5118,22 +5118,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5163,25 +5163,21 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-01-17T09:16:10.204614Z</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5196,7 +5192,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -5226,17 +5222,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -5244,26 +5240,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -5273,7 +5269,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5289,26 +5285,30 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>2025-12-26T23:53:31.459246Z</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5362,12 +5362,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5421,12 +5421,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5480,12 +5480,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5539,12 +5539,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5598,12 +5598,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5657,26 +5657,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5716,12 +5716,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5775,32 +5775,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5820,12 +5820,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5834,12 +5834,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -5893,12 +5893,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -5952,12 +5952,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6011,22 +6011,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6070,36 +6070,36 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6115,38 +6115,36 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>10</v>
-      </c>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6176,26 +6174,28 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6249,7 +6249,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6308,12 +6308,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6367,36 +6367,36 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6426,12 +6426,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6485,12 +6485,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6544,36 +6544,36 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6603,12 +6603,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -6628,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>3600</v>
+        <v>120</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6662,22 +6662,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6707,12 +6707,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6721,12 +6721,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -6780,12 +6780,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6839,12 +6839,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -6898,22 +6898,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -6943,23 +6943,21 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="n">
-        <v>58</v>
-      </c>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6974,7 +6972,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -7004,23 +7002,23 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7035,7 +7033,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7065,38 +7063,38 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -7106,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7115,7 +7113,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -7126,26 +7124,28 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="O113" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7165,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7199,12 +7199,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7258,12 +7258,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7317,36 +7317,36 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7376,12 +7376,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7435,12 +7435,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7494,12 +7494,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7553,12 +7553,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7612,12 +7612,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7671,12 +7671,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7730,12 +7730,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7848,12 +7848,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7907,12 +7907,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7966,12 +7966,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8099,14 +8099,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E130" t="b">
         <v>1</v>
       </c>
       <c r="F130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E132" t="b">
         <v>1</v>
       </c>
       <c r="F132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8261,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8379,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8556,12 +8556,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8630,14 +8630,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
         <v>1</v>
       </c>
       <c r="F139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8748,14 +8748,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E141" t="b">
         <v>1</v>
       </c>
       <c r="F141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8792,12 +8792,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -8910,12 +8910,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -8969,12 +8969,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9028,36 +9028,36 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9073,23 +9073,21 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="n">
-        <v>1</v>
-      </c>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9104,7 +9102,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9134,23 +9132,23 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9165,7 +9163,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9195,23 +9193,23 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9226,7 +9224,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9256,38 +9254,38 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9317,36 +9315,38 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9356,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9390,12 +9390,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9449,7 +9449,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9508,7 +9508,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9567,12 +9567,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9626,7 +9626,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9685,7 +9685,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9744,7 +9744,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9803,12 +9803,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -9862,12 +9862,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -9921,12 +9921,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -9980,22 +9980,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -10005,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10025,12 +10025,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10039,36 +10039,36 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10098,12 +10098,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10157,12 +10157,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10216,12 +10216,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10275,12 +10275,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10334,12 +10334,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10393,36 +10393,36 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10452,22 +10452,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10477,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -10497,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10570,22 +10570,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10688,7 +10688,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10747,36 +10747,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10806,12 +10806,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10865,36 +10865,36 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E177" t="b">
         <v>1</v>
       </c>
       <c r="F177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10924,12 +10924,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10983,12 +10983,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11042,12 +11042,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11064,7 +11064,7 @@
         <v>1</v>
       </c>
       <c r="F180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
         <v>1</v>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11101,22 +11101,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11160,12 +11160,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,12 +11219,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,12 +11278,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11337,12 +11337,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11396,12 +11396,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11455,12 +11455,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,41 +11514,41 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -11559,23 +11559,21 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="n">
-        <v>40</v>
-      </c>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11590,7 +11588,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11620,23 +11618,23 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11651,7 +11649,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11681,38 +11679,38 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11742,26 +11740,28 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="O191" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11815,12 +11815,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -11860,12 +11860,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11874,7 +11874,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11933,7 +11933,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11992,12 +11992,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12051,12 +12051,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12110,12 +12110,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -12155,12 +12155,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12169,12 +12169,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -12214,12 +12214,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12228,12 +12228,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12287,12 +12287,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -12346,29 +12346,29 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>1</v>
@@ -12391,12 +12391,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -12405,12 +12405,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12450,12 +12450,12 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
@@ -12464,12 +12464,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -12523,12 +12523,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12582,22 +12582,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -12627,16 +12627,75 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E207" t="b">
+        <v>1</v>
+      </c>
+      <c r="F207" t="b">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O207"/>
+  <dimension ref="A1:O217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,12 +2103,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2118,14 +2118,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2177,14 +2177,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2354,14 +2354,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2398,41 +2398,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2443,57 +2443,55 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>80</v>
-      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -2504,57 +2502,55 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>60</v>
-      </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2565,57 +2561,55 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>43</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -2626,12 +2620,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2640,36 +2634,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2685,12 +2679,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2699,26 +2693,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -2728,7 +2722,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2744,12 +2738,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2758,22 +2752,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -2783,11 +2777,11 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2803,12 +2797,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2817,36 +2811,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2862,12 +2856,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2876,36 +2870,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2921,12 +2915,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2935,22 +2929,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2960,11 +2954,11 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2980,12 +2974,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2994,32 +2988,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3028,7 +3022,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -3039,46 +3033,48 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3087,7 +3083,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -3098,46 +3094,48 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3146,7 +3144,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -3157,46 +3155,48 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3230,32 +3230,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3289,32 +3289,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3348,12 +3348,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3407,12 +3407,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3584,12 +3584,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3643,12 +3643,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3702,12 +3702,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3761,12 +3761,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3820,12 +3820,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3879,12 +3879,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3938,12 +3938,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3997,12 +3997,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4115,12 +4115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4130,17 +4130,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4174,12 +4174,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4189,17 +4189,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4292,12 +4292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4410,12 +4410,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4528,12 +4528,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4587,12 +4587,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4705,12 +4705,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4764,12 +4764,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5118,12 +5118,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5177,32 +5177,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5222,50 +5222,46 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2025-12-27T13:31:32.593277Z</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5285,40 +5281,36 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2025-12-27T13:31:33.294716Z</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5328,11 +5320,11 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5348,12 +5340,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5362,22 +5354,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5387,11 +5379,11 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5407,12 +5399,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5421,26 +5413,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -5450,7 +5442,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5466,12 +5458,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5480,26 +5472,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -5509,7 +5501,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5525,12 +5517,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5539,26 +5531,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -5568,7 +5560,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5584,12 +5576,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5598,26 +5590,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -5627,7 +5619,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5643,12 +5635,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5657,26 +5649,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -5686,7 +5678,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5702,12 +5694,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5716,22 +5708,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5741,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5761,12 +5753,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5775,7 +5767,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5785,12 +5777,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5820,46 +5812,50 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>2025-12-26T23:53:32.288215Z</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5879,50 +5875,54 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>2025-12-26T23:53:31.459246Z</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E93" t="b">
         <v>1</v>
       </c>
       <c r="F93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -5952,36 +5952,36 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E94" t="b">
         <v>1</v>
       </c>
       <c r="F94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6011,36 +6011,36 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E95" t="b">
         <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6070,12 +6070,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E96" t="b">
         <v>1</v>
       </c>
       <c r="F96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6129,36 +6129,36 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6174,52 +6174,50 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>10</v>
-      </c>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6235,12 +6233,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6249,36 +6247,36 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6294,12 +6292,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6308,12 +6306,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6323,7 +6321,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -6333,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6353,12 +6351,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6367,12 +6365,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6382,7 +6380,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -6392,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6412,12 +6410,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6426,22 +6424,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6455,7 +6453,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6471,12 +6469,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6485,22 +6483,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -6514,7 +6512,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6530,12 +6528,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6544,22 +6542,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -6573,7 +6571,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6589,12 +6587,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6603,32 +6601,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6648,12 +6646,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6662,36 +6660,36 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6707,12 +6705,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6721,22 +6719,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6766,36 +6764,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6839,22 +6839,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -6898,22 +6898,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -6957,22 +6957,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -7002,57 +7002,55 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="n">
-        <v>58</v>
-      </c>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -7063,57 +7061,55 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="n">
-        <v>66</v>
-      </c>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -7124,52 +7120,50 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="n">
-        <v>84</v>
-      </c>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7185,12 +7179,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7199,12 +7193,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7214,7 +7208,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7224,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7233,7 +7227,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -7244,12 +7238,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7258,12 +7252,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7273,7 +7267,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7283,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7303,12 +7297,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7317,22 +7311,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7362,12 +7356,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7376,36 +7370,36 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7421,12 +7415,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7435,36 +7429,36 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7480,12 +7474,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7494,36 +7488,36 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7539,12 +7533,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7553,41 +7547,41 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -7598,55 +7592,57 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -7657,55 +7653,57 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -7716,50 +7714,52 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7789,41 +7789,41 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7848,36 +7848,36 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7907,36 +7907,36 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7966,12 +7966,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8158,14 +8158,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E131" t="b">
         <v>1</v>
       </c>
       <c r="F131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E132" t="b">
         <v>1</v>
       </c>
       <c r="F132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8261,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8379,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8556,12 +8556,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
         <v>1</v>
       </c>
       <c r="F140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8792,12 +8792,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8807,14 +8807,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E142" t="b">
         <v>1</v>
       </c>
       <c r="F142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -8910,12 +8910,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -8969,12 +8969,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9028,12 +9028,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9087,36 +9087,36 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9132,52 +9132,50 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="n">
-        <v>1</v>
-      </c>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9193,52 +9191,50 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="n">
-        <v>73</v>
-      </c>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9254,42 +9250,40 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
-      <c r="O149" t="n">
-        <v>99</v>
-      </c>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" t="b">
         <v>0</v>
@@ -9299,7 +9293,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9315,42 +9309,40 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
-      <c r="O150" t="n">
-        <v>89</v>
-      </c>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="b">
         <v>0</v>
@@ -9360,7 +9352,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9376,12 +9368,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9390,36 +9382,36 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9435,12 +9427,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9449,36 +9441,36 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9494,12 +9486,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9508,36 +9500,36 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9553,12 +9545,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9567,36 +9559,36 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9612,12 +9604,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9626,36 +9618,36 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9671,12 +9663,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9685,7 +9677,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9695,12 +9687,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9730,21 +9722,23 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9754,12 +9748,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -9789,21 +9783,23 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+      <c r="O158" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9813,12 +9809,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -9848,36 +9844,38 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -9907,36 +9905,38 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+      <c r="O160" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -9980,12 +9980,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -10005,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10025,12 +10025,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10039,22 +10039,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -10084,12 +10084,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10098,36 +10098,36 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>1</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10157,36 +10157,36 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10216,36 +10216,36 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10275,36 +10275,36 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10334,36 +10334,36 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10393,36 +10393,36 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10452,12 +10452,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10477,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -10497,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10511,22 +10511,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10570,22 +10570,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10629,22 +10629,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10654,7 +10654,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10688,36 +10688,36 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10747,36 +10747,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10806,12 +10806,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10865,12 +10865,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10924,36 +10924,36 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E178" t="b">
         <v>1</v>
       </c>
       <c r="F178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10983,36 +10983,36 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E179" t="b">
         <v>1</v>
       </c>
       <c r="F179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11042,32 +11042,32 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" t="b">
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11101,29 +11101,29 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -11146,12 +11146,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11160,36 +11160,36 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,36 +11219,36 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,36 +11278,36 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11337,36 +11337,36 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11396,12 +11396,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11455,12 +11455,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,36 +11514,36 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E188" t="b">
         <v>1</v>
       </c>
       <c r="F188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,26 +11573,26 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="b">
         <v>0</v>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -11618,42 +11618,40 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" t="n">
-        <v>40</v>
-      </c>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="b">
         <v>0</v>
@@ -11668,7 +11666,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -11679,45 +11677,43 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="n">
-        <v>90</v>
-      </c>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -11729,7 +11725,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -11740,57 +11736,55 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="n">
-        <v>97</v>
-      </c>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -11801,12 +11795,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11815,36 +11809,36 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11860,12 +11854,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11874,36 +11868,36 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11919,12 +11913,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11933,7 +11927,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11943,26 +11937,26 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>1</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11978,12 +11972,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11992,36 +11986,36 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12037,12 +12031,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12051,36 +12045,36 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
         <v>1</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12096,12 +12090,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12110,36 +12104,36 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12155,12 +12149,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12169,22 +12163,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12214,36 +12208,38 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
+      <c r="O199" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12262,7 +12258,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -12273,36 +12269,38 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
+      <c r="O200" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12321,7 +12319,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -12332,26 +12330,28 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
+      <c r="O201" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -12391,12 +12391,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -12405,29 +12405,29 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
         <v>1</v>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
@@ -12464,29 +12464,29 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -12509,12 +12509,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -12523,29 +12523,29 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
         <v>1</v>
@@ -12568,12 +12568,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12582,29 +12582,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -12641,36 +12641,36 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
         <v>1</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -12686,16 +12686,606 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+        </is>
+      </c>
+      <c r="E208" t="b">
+        <v>0</v>
+      </c>
+      <c r="F208" t="b">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2022-12-12T15:42:56.669675Z</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2022-12-12T15:42:56.669675Z</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+        </is>
+      </c>
+      <c r="E209" t="b">
+        <v>0</v>
+      </c>
+      <c r="F209" t="b">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>{'email_routing': True, 'read_only': True}</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2025-03-14T01:50:15.254316Z</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2025-03-14T01:50:15.254316Z</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>_dmarc.videodioggi.com</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+        </is>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="b">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.516418Z</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.516418Z</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>*._domainkey.videodioggi.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>v=DKIM1; p=</t>
+        </is>
+      </c>
+      <c r="E211" t="b">
+        <v>0</v>
+      </c>
+      <c r="F211" t="b">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.509152Z</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.509152Z</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>videodioggi.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>v=spf1 -all</t>
+        </is>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+      <c r="F212" t="b">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.51106Z</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2021-12-12T16:20:23.51106Z</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E213" t="b">
+        <v>1</v>
+      </c>
+      <c r="F213" t="b">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2023-03-30T09:59:11.98058Z</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2023-03-30T09:59:12.228482Z</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>test2.webtek.live</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E214" t="b">
+        <v>1</v>
+      </c>
+      <c r="F214" t="b">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:29.902515Z</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2023-03-28T08:34:30.164318Z</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>432df2553b443742f9f905e155878536</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>test.webtek.live</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E215" t="b">
+        <v>1</v>
+      </c>
+      <c r="F215" t="b">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.078812Z</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2023-03-24T11:44:15.367412Z</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>webtek.live</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E216" t="b">
+        <v>1</v>
+      </c>
+      <c r="F216" t="b">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E217" t="b">
+        <v>1</v>
+      </c>
+      <c r="F217" t="b">
+        <v>1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O217"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,12 +1153,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c4b015ebb6540fa1c64482131c937ad9</t>
+          <t>371757d3dbe711ba7988b68768b3e3a0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>_acme-challenge.audiolibri.org</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>u0r8f2zhwT-M2O_kj3315TrScc29-R7LlP7PVb_dBPI</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:26.735522Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:57.512009Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1212,12 +1212,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8123b69792536eda89581575fc5e6501</t>
+          <t>c4b015ebb6540fa1c64482131c937ad9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>_dmarc.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:38.385312Z</t>
+          <t>2022-01-24T18:09:26.735522Z</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:01.139092Z</t>
+          <t>2026-02-23T09:20:57.512009Z</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1271,32 +1271,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
+          <t>8123b69792536eda89581575fc5e6501</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>www.certmate.org</t>
+          <t>_dmarc.audiolibri.org</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>185.199.109.153</t>
+          <t>v=DMARC1; p=reject</t>
         </is>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2025-07-01T16:44:05.723652Z</t>
+          <t>2022-01-24T18:09:38.385312Z</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2025-07-01T16:47:41.146282Z</t>
+          <t>2026-02-23T09:21:01.139092Z</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1330,29 +1330,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9a0c1ea7682256e45af5f83341fb113e</t>
+          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>www.certmate.org</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>185.199.109.153</t>
         </is>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1375,23 +1375,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:44:05.723652Z</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:47:41.146282Z</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>34</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aecf0cef3bc28aa58695c24be19d992c</t>
+          <t>9a0c1ea7682256e45af5f83341fb113e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1406,7 +1404,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1436,23 +1434,23 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fd67f08c9417a7d074fabd7e5513f715</t>
+          <t>aecf0cef3bc28aa58695c24be19d992c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1467,7 +1465,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1497,38 +1495,38 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14ecb7082a212233d816e345eea11668</t>
+          <t>fd67f08c9417a7d074fabd7e5513f715</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>test.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ns-858.awsdns-43.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1547,7 +1545,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1558,21 +1556,23 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0b4d1e1437d207800341e642f54e492f</t>
+          <t>14ecb7082a212233d816e345eea11668</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ns-8.awsdns-01.com</t>
+          <t>ns-858.awsdns-43.net</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
+          <t>0b4d1e1437d207800341e642f54e492f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ns-1790.awsdns-31.co.uk</t>
+          <t>ns-8.awsdns-01.com</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>759120960fb1797f3ceb20a074397a60</t>
+          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ns-1479.awsdns-56.org</t>
+          <t>ns-1790.awsdns-31.co.uk</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1749,22 +1749,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>abd1e138555a9935af96e12e735ae62e</t>
+          <t>759120960fb1797f3ceb20a074397a60</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>test.certmate.org</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>ns-1479.awsdns-56.org</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1808,12 +1808,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
+          <t>abd1e138555a9935af96e12e735ae62e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1867,41 +1867,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>cf2024-1._domainkey.certmate.org</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1926,12 +1926,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1941,14 +1941,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -1985,12 +1985,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2044,12 +2044,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>e5fcf6b15716297a5d2186248ae9a854</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>poc.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2118,14 +2118,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>poc-t1.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>poc-t2.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>864de75a873870b7681170b09d376c13</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>poc-t3.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1b02a47cd362942d252c1b985894c35a</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>poc-t4.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2398,12 +2398,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>495419b8c428fd1f648d0429a17fbe1c</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>poc-t5.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2457,12 +2457,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>c299e7513c4d25b2081f73236040cc69</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>poc-t6.cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>poc-t7.cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2575,12 +2575,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>86c96588cc20e61f4af5ebd8e1953428</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poc-t8.cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2634,12 +2634,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>recaptcha.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2693,12 +2693,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2708,14 +2708,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2752,12 +2752,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2811,12 +2811,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -2856,12 +2856,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2870,12 +2870,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2929,12 +2929,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2944,14 +2944,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2988,26 +2988,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -3033,23 +3033,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>80</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3064,7 +3062,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3094,23 +3092,23 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3125,7 +3123,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -3155,38 +3153,38 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3216,26 +3214,28 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3348,32 +3348,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3407,12 +3407,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3584,7 +3584,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3702,12 +3702,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3761,7 +3761,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3938,12 +3938,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3997,12 +3997,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4012,11 +4012,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4115,12 +4115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4174,12 +4174,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4292,12 +4292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4410,12 +4410,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4425,17 +4425,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4705,12 +4705,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4764,12 +4764,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5118,12 +5118,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5177,12 +5177,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5192,17 +5192,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -5236,12 +5236,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5295,12 +5295,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5354,12 +5354,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5413,12 +5413,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5472,12 +5472,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5531,12 +5531,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5590,12 +5590,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5649,12 +5649,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5708,12 +5708,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5767,22 +5767,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5812,25 +5812,21 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-01-17T09:16:10.204614Z</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5845,7 +5841,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5875,17 +5871,17 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
@@ -5893,26 +5889,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -5922,7 +5918,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5938,26 +5934,30 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>2025-12-26T23:53:31.459246Z</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6011,12 +6011,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6070,12 +6070,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6129,12 +6129,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -6188,12 +6188,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6247,12 +6247,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6306,26 +6306,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6365,12 +6365,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>_acme-challenge.edge99.net</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6424,32 +6424,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6483,32 +6483,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6542,12 +6542,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6601,12 +6601,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6660,22 +6660,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6719,29 +6719,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -6764,52 +6764,50 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="n">
-        <v>10</v>
-      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6825,12 +6823,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6839,7 +6837,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6849,12 +6847,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6884,26 +6882,28 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -6957,12 +6957,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7016,36 +7016,36 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7075,36 +7075,36 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7134,12 +7134,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7193,36 +7193,36 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7252,36 +7252,36 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7311,22 +7311,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7356,12 +7356,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7370,22 +7370,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7429,12 +7429,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7488,12 +7488,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7547,22 +7547,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -7592,38 +7592,36 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="n">
-        <v>58</v>
-      </c>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -7642,7 +7640,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -7653,23 +7651,21 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="n">
-        <v>66</v>
-      </c>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7684,7 +7680,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7714,38 +7710,38 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7755,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -7764,7 +7760,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -7775,36 +7771,38 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7834,26 +7832,28 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -7873,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -7907,12 +7907,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7952,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7966,36 +7966,36 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8025,36 +8025,36 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8261,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8379,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8556,12 +8556,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8748,14 +8748,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E141" t="b">
         <v>1</v>
       </c>
       <c r="F141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8792,12 +8792,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8807,14 +8807,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E142" t="b">
         <v>1</v>
       </c>
       <c r="F142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8866,14 +8866,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E143" t="b">
         <v>1</v>
       </c>
       <c r="F143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -8910,12 +8910,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E144" t="b">
         <v>1</v>
       </c>
       <c r="F144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -8969,12 +8969,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9028,12 +9028,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9087,12 +9087,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9146,12 +9146,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9205,12 +9205,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9264,12 +9264,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E150" t="b">
         <v>1</v>
       </c>
       <c r="F150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9323,12 +9323,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9338,14 +9338,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E151" t="b">
         <v>1</v>
       </c>
       <c r="F151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -9368,12 +9368,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9382,12 +9382,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9397,14 +9397,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E152" t="b">
         <v>1</v>
       </c>
       <c r="F152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9441,12 +9441,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E153" t="b">
         <v>1</v>
       </c>
       <c r="F153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9500,12 +9500,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9559,12 +9559,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9618,12 +9618,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9677,36 +9677,36 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9722,52 +9722,50 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
-      <c r="O157" t="n">
-        <v>1</v>
-      </c>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9783,23 +9781,21 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="n">
-        <v>73</v>
-      </c>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9814,7 +9810,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -9844,23 +9840,23 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9875,7 +9871,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -9905,38 +9901,38 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -9966,36 +9962,38 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="O161" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -10005,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10025,36 +10023,38 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -10098,12 +10098,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10157,7 +10157,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10216,12 +10216,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10275,12 +10275,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10334,7 +10334,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10393,7 +10393,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10452,12 +10452,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10511,12 +10511,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10570,12 +10570,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10629,22 +10629,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10654,7 +10654,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10688,36 +10688,36 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10747,36 +10747,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10806,12 +10806,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10865,12 +10865,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10924,12 +10924,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10983,12 +10983,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11042,36 +11042,36 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11101,36 +11101,36 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11160,22 +11160,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11185,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,22 +11219,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,22 +11278,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11337,7 +11337,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11396,36 +11396,36 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11455,36 +11455,36 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
         <v>1</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,36 +11514,36 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E188" t="b">
         <v>1</v>
       </c>
       <c r="F188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,36 +11573,36 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E189" t="b">
         <v>1</v>
       </c>
       <c r="F189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11632,12 +11632,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11691,12 +11691,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11713,7 +11713,7 @@
         <v>1</v>
       </c>
       <c r="F191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11750,36 +11750,36 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E192" t="b">
         <v>1</v>
       </c>
       <c r="F192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11809,22 +11809,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11868,12 +11868,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11927,12 +11927,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11986,12 +11986,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12045,22 +12045,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>rivoluzioneinformatica.org</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
           <t>www.rivoluzioneinformatica.org</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>CNAME</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12104,12 +12104,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12163,41 +12163,41 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -12208,57 +12208,55 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
-      <c r="O199" t="n">
-        <v>40</v>
-      </c>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
         <v>1</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -12269,23 +12267,21 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
-      <c r="O200" t="n">
-        <v>90</v>
-      </c>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12300,7 +12296,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12330,38 +12326,38 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12391,36 +12387,38 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
+      <c r="O202" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -12439,7 +12437,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -12450,26 +12448,28 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="O203" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -12509,12 +12509,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -12523,12 +12523,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12582,7 +12582,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -12641,12 +12641,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -12700,12 +12700,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
@@ -12759,12 +12759,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
@@ -12804,12 +12804,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
@@ -12818,12 +12818,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -12877,12 +12877,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -12922,12 +12922,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -12936,12 +12936,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -12981,12 +12981,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -12995,29 +12995,29 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -13040,12 +13040,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13054,29 +13054,29 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13113,12 +13113,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13172,12 +13172,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
@@ -13231,22 +13231,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13276,16 +13276,134 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>webtek.live</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>185.199.108.153</t>
+        </is>
+      </c>
+      <c r="E218" t="b">
+        <v>1</v>
+      </c>
+      <c r="F218" t="b">
+        <v>1</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2023-02-17T23:14:39.792808Z</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E219" t="b">
+        <v>1</v>
+      </c>
+      <c r="F219" t="b">
+        <v>1</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O219"/>
+  <dimension ref="A1:O220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,12 +11514,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>www.mixidaw.com</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T12:16:43.381049Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T18:58:28.024399Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,12 +11573,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11632,36 +11632,36 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E190" t="b">
         <v>1</v>
       </c>
       <c r="F190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11691,12 +11691,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11750,12 +11750,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11809,12 +11809,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11831,7 +11831,7 @@
         <v>1</v>
       </c>
       <c r="F193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -11854,12 +11854,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11868,22 +11868,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11927,12 +11927,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11986,12 +11986,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12045,12 +12045,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12104,12 +12104,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12163,12 +12163,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12208,12 +12208,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12222,12 +12222,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12267,12 +12267,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12281,41 +12281,41 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>1</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -12326,23 +12326,21 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
-      <c r="O201" t="n">
-        <v>40</v>
-      </c>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12357,7 +12355,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12387,23 +12385,23 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12418,7 +12416,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -12448,38 +12446,38 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -12509,26 +12507,28 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
+      <c r="O204" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
@@ -12568,12 +12568,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12582,12 +12582,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -12641,7 +12641,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -12700,7 +12700,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
@@ -12759,12 +12759,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -12804,12 +12804,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
@@ -12818,12 +12818,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -12877,12 +12877,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -12922,12 +12922,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -12936,12 +12936,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
@@ -12981,12 +12981,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -12995,12 +12995,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13054,12 +13054,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13113,29 +13113,29 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13172,12 +13172,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
@@ -13231,12 +13231,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
@@ -13290,12 +13290,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13335,12 +13335,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
@@ -13349,22 +13349,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13394,16 +13394,75 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E220" t="b">
+        <v>1</v>
+      </c>
+      <c r="F220" t="b">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O220"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,36 +555,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
+          <t>0397fc473b0d26aec2c986e742f1fc22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>mnrv.aidevhost.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>7ccc8d68-cac2-4c34-8cd6-2d0351b4d37e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-04-14T08:16:41.823299Z</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-04-14T08:16:41.823299Z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
+          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -659,12 +659,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2026-02-23T09:20:55.788713Z</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2026-02-23T09:20:55.788713Z</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
+          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -718,12 +718,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:15.423313Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:54.530581Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -732,7 +732,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>66de4cd56c98d8faddaffb325bc296bd</t>
+          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -777,12 +777,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.147955Z</t>
+          <t>2025-12-27T19:42:15.423313Z</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:53.92293Z</t>
+          <t>2026-02-23T09:20:54.530581Z</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -791,12 +791,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2b8843986f866d3e99f4d6834382282e</t>
+          <t>66de4cd56c98d8faddaffb325bc296bd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>www.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -836,12 +836,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2025-12-27T19:42:16.147955Z</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2026-02-23T09:20:53.92293Z</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -850,7 +850,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a7884955fee4043702153da01228b09f</t>
+          <t>2b8843986f866d3e99f4d6834382282e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -895,12 +895,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.950308Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.922031Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -909,7 +909,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
+          <t>a7884955fee4043702153da01228b09f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -954,12 +954,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:17.693642Z</t>
+          <t>2025-12-27T19:42:16.950308Z</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.313669Z</t>
+          <t>2026-02-23T09:21:07.922031Z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -968,7 +968,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>401726adb31f75b18399e2039d73d307</t>
+          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:18.539481Z</t>
+          <t>2025-12-27T19:42:17.693642Z</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:06.591532Z</t>
+          <t>2026-02-23T09:21:07.313669Z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1027,32 +1027,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
+          <t>401726adb31f75b18399e2039d73d307</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>www.audiolibri.org</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1072,25 +1072,21 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
+          <t>2025-12-27T19:42:18.539481Z</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-02-23T09:21:06.591532Z</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
+          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1135,17 +1131,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1153,22 +1149,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>371757d3dbe711ba7988b68768b3e3a0</t>
+          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>_acme-challenge.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>u0r8f2zhwT-M2O_kj3315TrScc29-R7LlP7PVb_dBPI</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1178,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1198,26 +1194,30 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-29T17:57:07.71633Z</t>
+          <t>2026-02-23T09:20:58.143923Z</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-29T17:57:07.71633Z</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>2026-02-23T09:20:58.143923Z</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c4b015ebb6540fa1c64482131c937ad9</t>
+          <t>371757d3dbe711ba7988b68768b3e3a0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>_acme-challenge.audiolibri.org</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>u0r8f2zhwT-M2O_kj3315TrScc29-R7LlP7PVb_dBPI</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:26.735522Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:57.512009Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8123b69792536eda89581575fc5e6501</t>
+          <t>c4b015ebb6540fa1c64482131c937ad9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>_dmarc.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:38.385312Z</t>
+          <t>2022-01-24T18:09:26.735522Z</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:01.139092Z</t>
+          <t>2026-02-23T09:20:57.512009Z</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1330,32 +1330,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
+          <t>8123b69792536eda89581575fc5e6501</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>www.certmate.org</t>
+          <t>_dmarc.audiolibri.org</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>185.199.109.153</t>
+          <t>v=DMARC1; p=reject</t>
         </is>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2025-07-01T16:44:05.723652Z</t>
+          <t>2022-01-24T18:09:38.385312Z</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2025-07-01T16:47:41.146282Z</t>
+          <t>2026-02-23T09:21:01.139092Z</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1389,29 +1389,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9a0c1ea7682256e45af5f83341fb113e</t>
+          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>www.certmate.org</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>185.199.109.153</t>
         </is>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1434,23 +1434,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:44:05.723652Z</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:47:41.146282Z</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>34</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>aecf0cef3bc28aa58695c24be19d992c</t>
+          <t>9a0c1ea7682256e45af5f83341fb113e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1465,7 +1463,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1495,23 +1493,23 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fd67f08c9417a7d074fabd7e5513f715</t>
+          <t>aecf0cef3bc28aa58695c24be19d992c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1526,7 +1524,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1556,38 +1554,38 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14ecb7082a212233d816e345eea11668</t>
+          <t>fd67f08c9417a7d074fabd7e5513f715</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>test.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ns-858.awsdns-43.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1606,7 +1604,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1617,21 +1615,23 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0b4d1e1437d207800341e642f54e492f</t>
+          <t>14ecb7082a212233d816e345eea11668</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ns-8.awsdns-01.com</t>
+          <t>ns-858.awsdns-43.net</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
+          <t>0b4d1e1437d207800341e642f54e492f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ns-1790.awsdns-31.co.uk</t>
+          <t>ns-8.awsdns-01.com</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>759120960fb1797f3ceb20a074397a60</t>
+          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ns-1479.awsdns-56.org</t>
+          <t>ns-1790.awsdns-31.co.uk</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1808,22 +1808,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>abd1e138555a9935af96e12e735ae62e</t>
+          <t>759120960fb1797f3ceb20a074397a60</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>test.certmate.org</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>ns-1479.awsdns-56.org</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1867,12 +1867,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
+          <t>abd1e138555a9935af96e12e735ae62e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1926,41 +1926,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>cf2024-1._domainkey.certmate.org</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -1985,12 +1985,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2044,12 +2044,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>e5fcf6b15716297a5d2186248ae9a854</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>poc.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2177,14 +2177,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>poc-t1.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>poc-t2.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>864de75a873870b7681170b09d376c13</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>poc-t3.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2398,12 +2398,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1b02a47cd362942d252c1b985894c35a</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>poc-t4.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2457,12 +2457,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>495419b8c428fd1f648d0429a17fbe1c</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>poc-t5.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>c299e7513c4d25b2081f73236040cc69</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>poc-t6.cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2575,12 +2575,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poc-t7.cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2634,12 +2634,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>86c96588cc20e61f4af5ebd8e1953428</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poc-t8.cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2693,12 +2693,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>recaptcha.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2752,12 +2752,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2811,12 +2811,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2870,12 +2870,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2929,12 +2929,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2988,12 +2988,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3047,26 +3047,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -3092,23 +3092,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>80</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3123,7 +3121,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -3153,23 +3151,23 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3184,7 +3182,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3214,38 +3212,38 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -3275,26 +3273,28 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3348,12 +3348,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3407,32 +3407,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3540,17 +3540,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3584,7 +3584,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3761,12 +3761,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3997,12 +3997,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4071,11 +4071,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4115,12 +4115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4174,12 +4174,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4292,12 +4292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4528,12 +4528,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4764,12 +4764,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4941,12 +4941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5118,12 +5118,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5177,12 +5177,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -5236,12 +5236,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5295,12 +5295,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5354,12 +5354,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5413,12 +5413,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5472,12 +5472,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5531,12 +5531,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5590,12 +5590,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5649,12 +5649,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5708,12 +5708,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5767,12 +5767,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5826,22 +5826,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5871,25 +5871,21 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+          <t>2026-01-17T09:16:10.204614Z</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5904,7 +5900,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5934,17 +5930,17 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
@@ -5952,26 +5948,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -5981,7 +5977,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5997,26 +5993,30 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>2025-12-26T23:53:31.459246Z</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6070,12 +6070,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6129,12 +6129,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -6188,12 +6188,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6247,12 +6247,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6306,12 +6306,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6365,36 +6365,36 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>_acme-challenge.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6424,12 +6424,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>_acme-challenge.edge99.net</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6449,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6483,12 +6483,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6542,32 +6542,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6601,12 +6601,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6660,12 +6660,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6719,12 +6719,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -6778,22 +6778,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6837,36 +6837,36 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6882,38 +6882,36 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="n">
-        <v>10</v>
-      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6943,26 +6941,28 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7075,12 +7075,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7134,36 +7134,36 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7193,12 +7193,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7252,12 +7252,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7311,36 +7311,36 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7370,12 +7370,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>3600</v>
+        <v>120</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7429,22 +7429,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7454,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7474,12 +7474,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7488,12 +7488,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7547,12 +7547,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7606,12 +7606,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7665,22 +7665,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -7710,23 +7710,21 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="n">
-        <v>58</v>
-      </c>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7741,7 +7739,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -7771,23 +7769,23 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7802,7 +7800,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -7832,38 +7830,38 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -7873,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -7882,7 +7880,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -7893,26 +7891,28 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -7932,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7952,12 +7952,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -7966,12 +7966,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8084,36 +8084,36 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8261,12 +8261,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8379,12 +8379,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8556,12 +8556,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8792,12 +8792,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8866,14 +8866,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
         <v>1</v>
       </c>
       <c r="F143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -8910,12 +8910,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -8969,12 +8969,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8984,14 +8984,14 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E145" t="b">
         <v>1</v>
       </c>
       <c r="F145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9028,12 +9028,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9087,12 +9087,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9146,12 +9146,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9205,12 +9205,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9264,12 +9264,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9323,12 +9323,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9382,12 +9382,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9397,14 +9397,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E152" t="b">
         <v>1</v>
       </c>
       <c r="F152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9441,12 +9441,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9500,12 +9500,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9515,14 +9515,14 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E154" t="b">
         <v>1</v>
       </c>
       <c r="F154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -9545,12 +9545,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9559,12 +9559,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9618,12 +9618,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9677,12 +9677,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9736,12 +9736,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9795,36 +9795,36 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>1</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9840,23 +9840,21 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" t="n">
-        <v>1</v>
-      </c>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9871,7 +9869,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -9901,23 +9899,23 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9932,7 +9930,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -9962,23 +9960,23 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9993,7 +9991,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -10023,38 +10021,38 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -10084,36 +10082,38 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
+      <c r="O163" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -10157,12 +10157,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10182,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -10275,7 +10275,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -10334,12 +10334,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10393,7 +10393,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10452,7 +10452,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10570,12 +10570,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10629,12 +10629,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10688,12 +10688,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10747,22 +10747,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -10772,7 +10772,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -10792,12 +10792,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -10806,36 +10806,36 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -10865,12 +10865,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -10924,12 +10924,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -10983,12 +10983,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11042,12 +11042,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11101,12 +11101,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11160,36 +11160,36 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11219,22 +11219,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -11264,12 +11264,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11337,22 +11337,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11396,7 +11396,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11455,7 +11455,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11514,36 +11514,36 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>www.mixidaw.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-04-03T12:16:43.381049Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-04-03T18:58:28.024399Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11573,12 +11573,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>www.mixidaw.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T12:16:43.381049Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T18:58:28.024399Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11632,12 +11632,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11691,36 +11691,36 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E191" t="b">
         <v>1</v>
       </c>
       <c r="F191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11750,12 +11750,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -11809,12 +11809,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -11868,12 +11868,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11890,7 +11890,7 @@
         <v>1</v>
       </c>
       <c r="F194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -11927,22 +11927,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -11986,12 +11986,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12045,12 +12045,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12104,12 +12104,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12163,12 +12163,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12208,12 +12208,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12222,12 +12222,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12267,12 +12267,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12281,12 +12281,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -12340,41 +12340,41 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="n">
         <v>1</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -12385,23 +12385,21 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
-      <c r="O202" t="n">
-        <v>40</v>
-      </c>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12416,7 +12414,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -12446,23 +12444,23 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12477,7 +12475,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -12507,38 +12505,38 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -12568,26 +12566,28 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
+      <c r="O205" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -12641,12 +12641,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -12700,7 +12700,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -12804,12 +12804,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
@@ -12818,12 +12818,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -12877,12 +12877,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -12936,12 +12936,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
@@ -12981,12 +12981,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -12995,12 +12995,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J213" t="inlineStr"/>
@@ -13040,12 +13040,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13054,12 +13054,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13113,12 +13113,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13172,29 +13172,29 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
         <v>1</v>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
@@ -13231,12 +13231,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
@@ -13290,12 +13290,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13335,12 +13335,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
@@ -13349,12 +13349,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
@@ -13408,22 +13408,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E220" t="b">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13453,16 +13453,75 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E221" t="b">
+        <v>1</v>
+      </c>
+      <c r="F221" t="b">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -629,12 +629,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2955ed5367089c641216b296f48c5402</t>
+          <t>8846758816f8bad11a7a46eb58498e7c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva-preprod.aidevhost.com</t>
+          <t>minerva-gcp.aidevhost.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
+          <t>d01e442f-e4cd-4805-a504-85eb77797b3a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -666,7 +666,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Managed by Terraform — Rollback access for migration 2026-05-02 (remove T+7)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -674,27 +678,31 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-15T22:01:19.663722Z</t>
+          <t>2026-05-02T19:25:30.420813Z</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-15T22:01:19.663722Z</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>2026-05-02T19:25:30.420813Z</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-02T19:25:30.420813Z</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>167eaa4b6cdb7183cbe6b40c8be16541</t>
+          <t>2955ed5367089c641216b296f48c5402</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minerva-prod.aidevhost.com</t>
+          <t>minerva-preprod.aidevhost.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -704,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>d01e442f-e4cd-4805-a504-85eb77797b3a.cfargotunnel.com</t>
+          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -726,11 +734,7 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Managed by Terraform — Minerva prod via Cloudflare Tunnel</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -738,31 +742,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-15T18:52:55.235456Z</t>
+          <t>2026-04-15T22:01:19.663722Z</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-15T18:52:55.235456Z</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-04-15T18:52:55.235456Z</t>
-        </is>
-      </c>
+          <t>2026-04-15T22:01:19.663722Z</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0397fc473b0d26aec2c986e742f1fc22</t>
+          <t>167eaa4b6cdb7183cbe6b40c8be16541</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mnrv.aidevhost.com</t>
+          <t>minerva-prod.aidevhost.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7ccc8d68-cac2-4c34-8cd6-2d0351b4d37e.cfargotunnel.com</t>
+          <t>f2b3ca2a-b25f-4529-8aa6-008e1f7ba3c5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -794,7 +794,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Managed by Terraform — Minerva prod via Cloudflare Tunnel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -802,15 +806,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-14T08:16:41.823299Z</t>
+          <t>2026-04-15T18:52:55.235456Z</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-14T08:16:41.823299Z</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>2026-05-02T21:28:44.063604Z</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-15T18:52:55.235456Z</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P224"/>
+  <dimension ref="A1:P225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,36 +2219,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>a2f19ece8ecd17be41ef5df6ea93c77e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>_dmarc.certmate.org</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>"v=DMARC1; p=none; rua=mailto:3f368183f1a544e1978df05d72916646@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2279,12 +2279,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2294,14 +2294,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2399,12 +2399,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2459,12 +2459,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>e5fcf6b15716297a5d2186248ae9a854</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>poc.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,14 +2474,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2519,12 +2519,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>poc-t1.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2579,12 +2579,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>poc-t2.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>864de75a873870b7681170b09d376c13</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poc-t3.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1b02a47cd362942d252c1b985894c35a</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poc-t4.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2759,12 +2759,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>495419b8c428fd1f648d0429a17fbe1c</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>poc-t5.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c299e7513c4d25b2081f73236040cc69</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>poc-t6.cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2879,12 +2879,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>poc-t7.cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2939,12 +2939,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>86c96588cc20e61f4af5ebd8e1953428</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>poc-t8.cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2999,12 +2999,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>recaptcha.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3119,12 +3119,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3179,12 +3179,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3194,14 +3194,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3239,12 +3239,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3299,12 +3299,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3359,26 +3359,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3404,24 +3404,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>80</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3436,7 +3434,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -3466,24 +3464,24 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3498,7 +3496,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -3528,39 +3526,39 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3590,27 +3588,29 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3725,32 +3725,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3785,12 +3785,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3845,12 +3845,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4085,12 +4085,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4145,7 +4145,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4325,12 +4325,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4340,17 +4340,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4385,12 +4385,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4400,11 +4400,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4445,12 +4445,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4505,12 +4505,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4565,12 +4565,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4685,12 +4685,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4805,12 +4805,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4820,17 +4820,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4865,12 +4865,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5105,12 +5105,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5165,12 +5165,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5225,12 +5225,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5285,12 +5285,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -5345,12 +5345,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5405,12 +5405,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5465,12 +5465,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5525,12 +5525,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5585,12 +5585,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5600,17 +5600,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5645,12 +5645,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5705,12 +5705,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5825,12 +5825,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5885,12 +5885,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5945,12 +5945,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6005,12 +6005,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -6065,12 +6065,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6125,12 +6125,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6185,22 +6185,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6230,26 +6230,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6264,7 +6260,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6294,18 +6290,18 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -6313,26 +6309,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
@@ -6342,7 +6338,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6358,27 +6354,31 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6433,12 +6433,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6493,12 +6493,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6553,12 +6553,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6613,12 +6613,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6673,12 +6673,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6733,36 +6733,36 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>_acme-challenge.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6793,12 +6793,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>_acme-challenge.edge99.net</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6853,12 +6853,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -6913,32 +6913,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6973,12 +6973,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -7093,12 +7093,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7153,22 +7153,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7213,36 +7213,36 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7258,39 +7258,37 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="n">
-        <v>10</v>
-      </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7320,27 +7318,29 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7395,7 +7395,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7455,12 +7455,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7515,36 +7515,36 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7575,12 +7575,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7635,12 +7635,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7695,36 +7695,36 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7755,12 +7755,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>3600</v>
+        <v>120</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7800,12 +7800,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7815,22 +7815,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7875,12 +7875,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7935,12 +7935,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7995,12 +7995,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -8055,22 +8055,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -8100,24 +8100,22 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="n">
-        <v>58</v>
-      </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8132,7 +8130,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8162,24 +8160,24 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8194,7 +8192,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8224,39 +8222,39 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -8266,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8275,7 +8273,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -8286,27 +8284,29 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8361,12 +8361,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8421,12 +8421,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8466,12 +8466,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8481,36 +8481,36 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
         <v>1</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8541,12 +8541,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8661,12 +8661,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8721,12 +8721,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8781,12 +8781,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8841,12 +8841,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8961,12 +8961,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -9021,12 +9021,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -9081,12 +9081,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -9141,12 +9141,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9201,12 +9201,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9261,12 +9261,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E147" t="b">
         <v>1</v>
       </c>
       <c r="F147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -9306,12 +9306,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9321,12 +9321,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9381,12 +9381,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9396,14 +9396,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E149" t="b">
         <v>1</v>
       </c>
       <c r="F149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9441,12 +9441,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9501,12 +9501,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9561,12 +9561,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9621,12 +9621,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9681,12 +9681,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9741,12 +9741,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9801,12 +9801,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9816,14 +9816,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E156" t="b">
         <v>1</v>
       </c>
       <c r="F156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9861,12 +9861,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9921,12 +9921,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9936,14 +9936,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E158" t="b">
         <v>1</v>
       </c>
       <c r="F158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9981,12 +9981,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -10041,12 +10041,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -10101,12 +10101,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -10146,12 +10146,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -10161,12 +10161,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10221,36 +10221,36 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10266,24 +10266,22 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="n">
-        <v>1</v>
-      </c>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10298,7 +10296,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10328,24 +10326,24 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10360,7 +10358,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10390,24 +10388,24 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10422,7 +10420,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -10452,39 +10450,39 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -10514,37 +10512,39 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
+      <c r="P167" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -10554,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10589,12 +10589,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -10614,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10649,7 +10649,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10709,7 +10709,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10769,12 +10769,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10829,7 +10829,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10889,7 +10889,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10949,7 +10949,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -11009,12 +11009,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -11069,12 +11069,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -11129,12 +11129,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -11189,22 +11189,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11249,36 +11249,36 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11309,12 +11309,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11369,12 +11369,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11414,12 +11414,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11429,12 +11429,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11489,12 +11489,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11549,12 +11549,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11609,36 +11609,36 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11669,22 +11669,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11694,7 +11694,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11729,7 +11729,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11789,22 +11789,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11849,7 +11849,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11909,7 +11909,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11969,36 +11969,36 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>www.mixidaw.com</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12014,12 +12014,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-04-03T12:16:43.381049Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-04-03T18:58:28.024399Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -12029,12 +12029,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>www.mixidaw.com</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T12:16:43.381049Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2026-04-03T18:58:28.024399Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -12089,12 +12089,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12134,12 +12134,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -12149,36 +12149,36 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E195" t="b">
         <v>1</v>
       </c>
       <c r="F195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>1</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -12209,12 +12209,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12269,12 +12269,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12314,12 +12314,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12329,12 +12329,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12351,7 +12351,7 @@
         <v>1</v>
       </c>
       <c r="F198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12389,22 +12389,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12449,12 +12449,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12509,12 +12509,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -12569,12 +12569,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -12629,12 +12629,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
@@ -12689,12 +12689,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -12749,12 +12749,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12809,41 +12809,41 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -12854,24 +12854,22 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="n">
-        <v>40</v>
-      </c>
+      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12886,7 +12884,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -12916,24 +12914,24 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12948,7 +12946,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -12978,39 +12976,39 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -13040,27 +13038,29 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
+      <c r="P209" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -13100,12 +13100,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -13280,12 +13280,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13295,12 +13295,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -13340,12 +13340,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13355,12 +13355,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -13400,12 +13400,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13415,12 +13415,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
@@ -13460,12 +13460,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
@@ -13475,12 +13475,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -13580,12 +13580,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
@@ -13595,12 +13595,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
@@ -13655,29 +13655,29 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
         <v>1</v>
@@ -13700,12 +13700,12 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
@@ -13715,12 +13715,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
@@ -13775,12 +13775,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -13835,12 +13835,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13880,12 +13880,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
@@ -13895,22 +13895,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E224" t="b">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -13940,17 +13940,77 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E225" t="b">
+        <v>1</v>
+      </c>
+      <c r="F225" t="b">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P225"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,12 +501,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7c927eef9664b42ce0e8b22e4c434a06</t>
+          <t>2c36fa790545cbccce9526eeafbce666</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>minerva.aidevhost.com</t>
+          <t>minerva-dev.aidevhost.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
+          <t>366e33f0-7e37-49b4-9ce2-507d05a35c12.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -538,7 +538,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Managed by Terraform — Minerva dev locale via CF Tunnel (Mac)</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -546,27 +550,31 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-08T15:21:59.158817Z</t>
+          <t>2026-04-15T20:55:30.46428Z</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T15:21:59.158817Z</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>2026-04-15T20:55:30.46428Z</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-04-15T20:55:30.46428Z</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2c36fa790545cbccce9526eeafbce666</t>
+          <t>8846758816f8bad11a7a46eb58498e7c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>minerva-dev.aidevhost.com</t>
+          <t>minerva-gcp.aidevhost.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -576,7 +584,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>366e33f0-7e37-49b4-9ce2-507d05a35c12.cfargotunnel.com</t>
+          <t>d01e442f-e4cd-4805-a504-85eb77797b3a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -600,7 +608,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Managed by Terraform — Minerva dev locale via CF Tunnel (Mac)</t>
+          <t>Managed by Terraform — Rollback access for migration 2026-05-02 (remove T+7)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -610,17 +618,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-15T20:55:30.46428Z</t>
+          <t>2026-05-02T19:25:30.420813Z</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-15T20:55:30.46428Z</t>
+          <t>2026-05-02T19:25:30.420813Z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-15T20:55:30.46428Z</t>
+          <t>2026-05-02T19:25:30.420813Z</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -629,12 +637,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8846758816f8bad11a7a46eb58498e7c</t>
+          <t>2955ed5367089c641216b296f48c5402</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva-gcp.aidevhost.com</t>
+          <t>minerva-preprod.aidevhost.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,7 +652,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>d01e442f-e4cd-4805-a504-85eb77797b3a.cfargotunnel.com</t>
+          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -666,11 +674,7 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Managed by Terraform — Rollback access for migration 2026-05-02 (remove T+7)</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -678,31 +682,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-05-02T19:25:30.420813Z</t>
+          <t>2026-04-15T22:01:19.663722Z</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-02T19:25:30.420813Z</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-05-02T19:25:30.420813Z</t>
-        </is>
-      </c>
+          <t>2026-04-15T22:01:19.663722Z</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2955ed5367089c641216b296f48c5402</t>
+          <t>167eaa4b6cdb7183cbe6b40c8be16541</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minerva-preprod.aidevhost.com</t>
+          <t>minerva-prod.aidevhost.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>936c93f6-65eb-4939-ba98-24d965f228b4.cfargotunnel.com</t>
+          <t>f2b3ca2a-b25f-4529-8aa6-008e1f7ba3c5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -734,7 +734,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Managed by Terraform — Minerva prod via Cloudflare Tunnel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -742,51 +746,55 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-15T22:01:19.663722Z</t>
+          <t>2026-04-15T18:52:55.235456Z</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-15T22:01:19.663722Z</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>2026-05-02T21:28:44.063604Z</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-04-15T18:52:55.235456Z</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>167eaa4b6cdb7183cbe6b40c8be16541</t>
+          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>minerva-prod.aidevhost.com</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>f2b3ca2a-b25f-4529-8aa6-008e1f7ba3c5.cfargotunnel.com</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -794,11 +802,7 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Managed by Terraform — Minerva prod via Cloudflare Tunnel</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -806,26 +810,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-15T18:52:55.235456Z</t>
+          <t>2026-02-23T09:20:55.788713Z</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-02T21:28:44.063604Z</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-04-15T18:52:55.235456Z</t>
-        </is>
-      </c>
+          <t>2026-02-23T09:20:55.788713Z</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0a390863d7e4ba6904c5205f98a2a5d2</t>
+          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -870,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.788713Z</t>
+          <t>2026-02-23T09:20:55.134017Z</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -885,7 +885,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0c1eaa4fed3dee3fe216b7eda2e9a2c8</t>
+          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -930,12 +930,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2025-12-27T19:42:15.423313Z</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:55.134017Z</t>
+          <t>2026-02-23T09:20:54.530581Z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f1ebea3204e85074be5e06aa68d2fa48</t>
+          <t>66de4cd56c98d8faddaffb325bc296bd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -990,12 +990,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:15.423313Z</t>
+          <t>2025-12-27T19:42:16.147955Z</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:54.530581Z</t>
+          <t>2026-02-23T09:20:53.92293Z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1005,12 +1005,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>66de4cd56c98d8faddaffb325bc296bd</t>
+          <t>2b8843986f866d3e99f4d6834382282e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>www.audiolibri.org</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.147955Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:53.92293Z</t>
+          <t>2026-02-23T09:21:08.51721Z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2b8843986f866d3e99f4d6834382282e</t>
+          <t>a7884955fee4043702153da01228b09f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2025-12-27T19:42:16.950308Z</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:08.51721Z</t>
+          <t>2026-02-23T09:21:07.922031Z</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a7884955fee4043702153da01228b09f</t>
+          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:16.950308Z</t>
+          <t>2025-12-27T19:42:17.693642Z</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.922031Z</t>
+          <t>2026-02-23T09:21:07.313669Z</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ce3007ccf8815fe015045c50dd3a5a00</t>
+          <t>401726adb31f75b18399e2039d73d307</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:17.693642Z</t>
+          <t>2025-12-27T19:42:18.539481Z</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:07.313669Z</t>
+          <t>2026-02-23T09:21:06.591532Z</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1245,32 +1245,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>401726adb31f75b18399e2039d73d307</t>
+          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>www.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1290,22 +1290,26 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2025-12-27T19:42:18.539481Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:06.591532Z</t>
+          <t>2026-02-23T09:20:59.121899Z</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>34ee6ce7fd8c2150087754ee41b63f09</t>
+          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1350,18 +1354,18 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
+          <t>2026-02-23T09:20:58.143923Z</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:59.121899Z</t>
+          <t>2026-02-23T09:20:58.143923Z</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1369,22 +1373,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>78cb4ae468fd7f7d2458590baccba8eb</t>
+          <t>371757d3dbe711ba7988b68768b3e3a0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>_acme-challenge.audiolibri.org</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>u0r8f2zhwT-M2O_kj3315TrScc29-R7LlP7PVb_dBPI</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1394,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1414,31 +1418,27 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:58.143923Z</t>
+          <t>2026-03-29T17:57:07.71633Z</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>371757d3dbe711ba7988b68768b3e3a0</t>
+          <t>c4b015ebb6540fa1c64482131c937ad9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>_acme-challenge.audiolibri.org</t>
+          <t>audiolibri.org</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>u0r8f2zhwT-M2O_kj3315TrScc29-R7LlP7PVb_dBPI</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-29T17:57:07.71633Z</t>
+          <t>2022-01-24T18:09:26.735522Z</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-29T17:57:07.71633Z</t>
+          <t>2026-02-23T09:20:57.512009Z</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1493,12 +1493,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c4b015ebb6540fa1c64482131c937ad9</t>
+          <t>8123b69792536eda89581575fc5e6501</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>audiolibri.org</t>
+          <t>_dmarc.audiolibri.org</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DMARC1; p=reject</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:26.735522Z</t>
+          <t>2022-01-24T18:09:38.385312Z</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:57.512009Z</t>
+          <t>2026-02-23T09:21:01.139092Z</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1553,32 +1553,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8123b69792536eda89581575fc5e6501</t>
+          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>_dmarc.audiolibri.org</t>
+          <t>www.certmate.org</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject</t>
+          <t>185.199.109.153</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2022-01-24T18:09:38.385312Z</t>
+          <t>2025-07-01T16:44:05.723652Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-23T09:21:01.139092Z</t>
+          <t>2025-07-01T16:47:41.146282Z</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1613,29 +1613,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
+          <t>9a0c1ea7682256e45af5f83341fb113e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>www.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>185.199.109.153</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1658,22 +1658,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2025-07-01T16:44:05.723652Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-07-01T16:47:41.146282Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9a0c1ea7682256e45af5f83341fb113e</t>
+          <t>aecf0cef3bc28aa58695c24be19d992c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1690,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1718,24 +1720,24 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aecf0cef3bc28aa58695c24be19d992c</t>
+          <t>fd67f08c9417a7d074fabd7e5513f715</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1750,7 +1752,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1780,39 +1782,39 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fd67f08c9417a7d074fabd7e5513f715</t>
+          <t>14ecb7082a212233d816e345eea11668</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>test.certmate.org</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>ns-858.awsdns-43.net</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1831,7 +1833,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1842,24 +1844,22 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>58</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14ecb7082a212233d816e345eea11668</t>
+          <t>0b4d1e1437d207800341e642f54e492f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ns-858.awsdns-43.net</t>
+          <t>ns-8.awsdns-01.com</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0b4d1e1437d207800341e642f54e492f</t>
+          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ns-8.awsdns-01.com</t>
+          <t>ns-1790.awsdns-31.co.uk</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1979,7 +1979,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
+          <t>759120960fb1797f3ceb20a074397a60</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ns-1790.awsdns-31.co.uk</t>
+          <t>ns-1479.awsdns-56.org</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2039,22 +2039,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>759120960fb1797f3ceb20a074397a60</t>
+          <t>abd1e138555a9935af96e12e735ae62e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>test.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ns-1479.awsdns-56.org</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2099,12 +2099,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abd1e138555a9935af96e12e735ae62e</t>
+          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>cf2024-1._domainkey.certmate.org</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2159,12 +2159,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
+          <t>a2f19ece8ecd17be41ef5df6ea93c77e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.certmate.org</t>
+          <t>_dmarc.certmate.org</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:3f368183f1a544e1978df05d72916646@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2219,36 +2219,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a2f19ece8ecd17be41ef5df6ea93c77e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>_dmarc.certmate.org</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:3f368183f1a544e1978df05d72916646@dmarc-reports.cloudflare.net"</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-05-04T08:08:44.893264Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05-04T08:08:44.893264Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2279,12 +2279,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2294,14 +2294,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2399,12 +2399,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2459,12 +2459,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,14 +2474,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2519,12 +2519,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>e5fcf6b15716297a5d2186248ae9a854</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>poc.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2579,12 +2579,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>poc-t1.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poc-t2.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>864de75a873870b7681170b09d376c13</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poc-t3.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2759,12 +2759,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1b02a47cd362942d252c1b985894c35a</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>poc-t4.cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>495419b8c428fd1f648d0429a17fbe1c</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>poc-t5.cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2879,12 +2879,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>c299e7513c4d25b2081f73236040cc69</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>poc-t6.cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2939,12 +2939,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>poc-t7.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2999,12 +2999,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>86c96588cc20e61f4af5ebd8e1953428</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>poc-t8.cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>recaptcha.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3119,12 +3119,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3179,12 +3179,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3194,14 +3194,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3239,12 +3239,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3299,12 +3299,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3359,26 +3359,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3404,22 +3404,24 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2025-12-13T22:19:39.326547Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3434,7 +3436,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -3464,24 +3466,24 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-13T22:19:39.315811Z</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b800160acc18139f7115d618ae0df907</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3496,7 +3498,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -3526,39 +3528,39 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.315811Z</t>
+          <t>2025-12-13T22:19:39.304361Z</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>b800160acc18139f7115d618ae0df907</t>
+          <t>6040974b5053a16191ddb8e50564d5d5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>cf2024-1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3588,29 +3590,27 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.304361Z</t>
+          <t>2025-12-13T22:19:39.346438Z</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>43</v>
-      </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6040974b5053a16191ddb8e50564d5d5</t>
+          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.cyberapi.io</t>
+          <t>cyberapi.io</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:19:39.336403Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.346438Z</t>
+          <t>2025-12-13T22:22:09.331366Z</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0a714114d6eb08eb253a239bbb8b26c5</t>
+          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>_dmarc.cyberapi.io</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net include:spf.mailtrap.live ~all"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.336403Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2025-12-13T22:22:09.331366Z</t>
+          <t>2025-12-13T22:12:23.116436Z</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3725,32 +3725,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>b41a98d6278e97fdaae7fd6a64edc776</t>
+          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>_dmarc.cyberapi.io</t>
+          <t>ap.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:dmarc@smtp-staging.mailtrap.net; ruf=mailto:dmarc@smtp-staging.mailtrap.net; rf=afrf; pct=100"</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:23.116436Z</t>
+          <t>2025-12-27T13:31:28.954647Z</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3785,12 +3785,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fd64e91b3d7277b594e10aa0b7e184e2</t>
+          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ap.cdn.edge99.net</t>
+          <t>argocd.edge99.net</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:28.954647Z</t>
+          <t>2026-01-17T09:16:07.490949Z</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3845,12 +3845,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>af1a523c4e78f97ad5c59a12ce309f20</t>
+          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>argocd.edge99.net</t>
+          <t>canary.edge99.net</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:07.490949Z</t>
+          <t>2026-01-17T09:13:31.387411Z</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>e6c9ca430b3b09c21b61a373dff6b193</t>
+          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2025-12-25T10:32:34.582168Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:31.387411Z</t>
+          <t>2026-01-17T09:13:30.79763Z</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>c73299ab28c1be5930cdca5c27ae5d75</t>
+          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-12-25T10:32:34.582168Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:30.79763Z</t>
+          <t>2025-12-27T10:24:43.675189Z</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2ec8c0b734a8846c32ef6ebc34fcbe9e</t>
+          <t>286231a61c9e04ed79191479a97d363d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.675189Z</t>
+          <t>2025-12-27T10:24:43.040146Z</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4085,12 +4085,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>286231a61c9e04ed79191479a97d363d</t>
+          <t>28ae5170c329a3aec750e89f1fc746ad</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>canary.edge99.net</t>
+          <t>cdn.edge99.net</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2025-12-27T10:24:43.040146Z</t>
+          <t>2026-01-17T09:13:32.634393Z</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4145,7 +4145,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28ae5170c329a3aec750e89f1fc746ad</t>
+          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2025-12-26T23:53:41.17051Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.634393Z</t>
+          <t>2026-01-17T09:13:32.008009Z</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>47d2b80bb85f3c9d2a29de6c71dd658f</t>
+          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.17051Z</t>
+          <t>2025-12-26T23:53:42.746797Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:32.008009Z</t>
+          <t>2026-01-02T16:11:32.508846Z</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bec47d6ece73e4b22bdd94e09dd37458</t>
+          <t>ab004065356f93519ec42f4d28626857</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:42.746797Z</t>
+          <t>2025-12-26T23:53:41.844611Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:32.508846Z</t>
+          <t>2026-01-02T16:11:31.768873Z</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4325,12 +4325,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ab004065356f93519ec42f4d28626857</t>
+          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>cdn.edge99.net</t>
+          <t>control.edge99.net</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4340,17 +4340,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>100.110.99.1</t>
         </is>
       </c>
       <c r="E65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:41.844611Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:31.768873Z</t>
+          <t>2025-12-27T00:09:48.763474Z</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4385,12 +4385,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dd9cda661a53ff7fcc22618ea2701b9a</t>
+          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>control.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4400,11 +4400,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>100.110.99.1</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2025-12-19T15:04:15.633073Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:48.763474Z</t>
+          <t>2026-01-02T16:11:29.52582Z</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4445,12 +4445,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>df7a3ddec69da98af45f8dbf5b5c59e4</t>
+          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>edge-arz.edge99.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2025-12-19T15:04:15.633073Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:29.52582Z</t>
+          <t>2026-01-17T09:13:35.856496Z</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4505,12 +4505,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>46d2468d26c30af32b63fa0b78f8fddf</t>
+          <t>1d4ae58f74e95387468d001cb5ede44e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>edge-arz.edge99.net</t>
+          <t>edge-hel.edge99.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.856496Z</t>
+          <t>2026-01-17T09:13:37.398436Z</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4565,12 +4565,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1d4ae58f74e95387468d001cb5ede44e</t>
+          <t>25308823ae2738c407f6fa8743bfde33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>edge-hel.edge99.net</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2025-12-26T23:53:46.520651Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:37.398436Z</t>
+          <t>2026-01-09T16:24:12.130657Z</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25308823ae2738c407f6fa8743bfde33</t>
+          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge-syd.edge99.net</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:46.520651Z</t>
+          <t>2025-12-26T23:53:47.745964Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.130657Z</t>
+          <t>2026-01-09T16:24:12.839331Z</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4685,12 +4685,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>e56f333078e2121fb2ac3f311c8b6df8</t>
+          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>edge-syd.edge99.net</t>
+          <t>eu.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:47.745964Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:12.839331Z</t>
+          <t>2026-01-17T09:13:33.878614Z</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dc7603fec8cac7dc7025ef7c77d2c4af</t>
+          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2025-12-27T13:31:29.703174Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.878614Z</t>
+          <t>2026-01-17T09:13:33.251695Z</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4805,12 +4805,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5c8b28263abb5086bbfcdd059f27ad0b</t>
+          <t>9361bf57919e2eb334aa91f608523d0d</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eu.cdn.edge99.net</t>
+          <t>gitlab.edge99.net</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4820,17 +4820,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:29.703174Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:33.251695Z</t>
+          <t>2025-12-27T00:09:49.376944Z</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4865,12 +4865,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9361bf57919e2eb334aa91f608523d0d</t>
+          <t>b428fd68dd7723ec82fc7fee2153b658</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gitlab.edge99.net</t>
+          <t>global.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>89.46.67.54</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:49.376944Z</t>
+          <t>2026-01-17T09:13:35.188243Z</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>b428fd68dd7723ec82fc7fee2153b658</t>
+          <t>52c0af421b8ea438edc8a40118e53cf4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>89.46.67.54</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2025-12-27T13:31:30.378986Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:35.188243Z</t>
+          <t>2026-01-17T09:13:34.509679Z</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>52c0af421b8ea438edc8a40118e53cf4</t>
+          <t>e77f748850a9219373b529301b8f118f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:30.378986Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:34.509679Z</t>
+          <t>2025-12-27T13:31:31.921357Z</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>e77f748850a9219373b529301b8f118f</t>
+          <t>71e5d4142066af8483577054c63fec8f</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.921357Z</t>
+          <t>2025-12-27T13:31:31.076316Z</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5105,12 +5105,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>71e5d4142066af8483577054c63fec8f</t>
+          <t>a2b861fc823c3b3b791efbdea34128db</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>global.cdn.edge99.net</t>
+          <t>gotify.edge99.net</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:31.076316Z</t>
+          <t>2026-01-09T16:24:13.446114Z</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5165,12 +5165,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>a2b861fc823c3b3b791efbdea34128db</t>
+          <t>8bd1b56900a669d97795c8f1158d2898</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gotify.edge99.net</t>
+          <t>grafana.edge99.net</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:13.446114Z</t>
+          <t>2025-12-27T00:10:33.245416Z</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5225,12 +5225,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8bd1b56900a669d97795c8f1158d2898</t>
+          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>grafana.edge99.net</t>
+          <t>harbor.edge99.net</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:33.245416Z</t>
+          <t>2026-01-17T09:16:08.146382Z</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5285,12 +5285,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>e3ebdc5e3351c519e35b53c2b9fbef8d</t>
+          <t>9bd8bb9154beef4473df4599131937a4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>harbor.edge99.net</t>
+          <t>infisical.edge99.net</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.98.95.74</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.146382Z</t>
+          <t>2025-12-27T00:09:50.04475Z</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -5345,12 +5345,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9bd8bb9154beef4473df4599131937a4</t>
+          <t>4b3ae3b8c8058fa848310ead4586f500</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>infisical.edge99.net</t>
+          <t>k3s.edge99.net</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>100.98.95.74</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:50.04475Z</t>
+          <t>2026-01-17T09:16:08.764859Z</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5405,12 +5405,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4b3ae3b8c8058fa848310ead4586f500</t>
+          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>k3s.edge99.net</t>
+          <t>live.edge99.net</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:08.764859Z</t>
+          <t>2026-01-10T22:49:54.731829Z</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5465,12 +5465,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3ef00bb56556f9766ed2dc7ba14d00ed</t>
+          <t>bb09c8365dbcafce6575094f2a401d9f</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>live.edge99.net</t>
+          <t>monitor.edge99.net</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-01-10T22:49:54.731829Z</t>
+          <t>2026-01-05T13:21:42.080054Z</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5525,12 +5525,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bb09c8365dbcafce6575094f2a401d9f</t>
+          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>monitor.edge99.net</t>
+          <t>n8n.edge99.net</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.97.70.3</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:42.080054Z</t>
+          <t>2026-02-23T09:20:50.514279Z</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5585,12 +5585,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>40641ed1ed76b78043b4ec33bfd33b57</t>
+          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>n8n.edge99.net</t>
+          <t>na.cdn.edge99.net</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5600,17 +5600,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>100.97.70.3</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:50.514279Z</t>
+          <t>2025-12-27T13:31:32.593277Z</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5645,12 +5645,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ad52fda9ae7d75a80f5b7f683c2f242c</t>
+          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>na.cdn.edge99.net</t>
+          <t>origin-ap.edge99.net</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>46.250.245.74</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:32.593277Z</t>
+          <t>2025-12-27T13:31:33.294716Z</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5705,12 +5705,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8a986e6fbf6cb724c8c40f6854f8e8e5</t>
+          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>origin-ap.edge99.net</t>
+          <t>origin-eu.edge99.net</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>46.250.245.74</t>
+          <t>65.109.163.154</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2025-12-27T13:31:33.924922Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.294716Z</t>
+          <t>2026-01-17T09:13:39.35235Z</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8799d5c2cd7af9f22ab31c14b808c8e3</t>
+          <t>6fb97126388ee3497dde75f9d2c65af6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>origin-eu.edge99.net</t>
+          <t>origin-na.edge99.net</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>65.109.163.154</t>
+          <t>51.222.140.163</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:33.924922Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-01-17T09:13:39.35235Z</t>
+          <t>2025-12-27T13:31:34.596506Z</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5825,12 +5825,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6fb97126388ee3497dde75f9d2c65af6</t>
+          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>origin-na.edge99.net</t>
+          <t>portal.edge99.net</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>51.222.140.163</t>
+          <t>100.122.88.46</t>
         </is>
       </c>
       <c r="E90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2025-12-27T13:31:34.596506Z</t>
+          <t>2026-01-05T13:21:43.343554Z</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5885,12 +5885,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2d3a5a3a78a89440cf05fc2578fdf937</t>
+          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>portal.edge99.net</t>
+          <t>prometheus.edge99.net</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>100.122.88.46</t>
+          <t>100.106.106.52</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-01-05T13:21:43.343554Z</t>
+          <t>2025-12-27T00:10:34.575724Z</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5945,12 +5945,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>51c56e5578a8f891177bcd98ea1bfc63</t>
+          <t>6f86af0a494ff0a16b086445dadb09e9</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>prometheus.edge99.net</t>
+          <t>registry.edge99.net</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>100.106.106.52</t>
+          <t>100.115.154.125</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2025-12-27T00:10:34.575724Z</t>
+          <t>2025-12-27T00:09:51.306371Z</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6005,12 +6005,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6f86af0a494ff0a16b086445dadb09e9</t>
+          <t>9c2664d0df87b9b00b19128a822779ff</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>registry.edge99.net</t>
+          <t>test.edge99.net</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>100.115.154.125</t>
+          <t>100.86.174.68</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2025-12-27T00:09:51.306371Z</t>
+          <t>2026-01-17T09:16:09.391479Z</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -6065,12 +6065,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9c2664d0df87b9b00b19128a822779ff</t>
+          <t>edbcd182eae447bdcb79d230631a2a7c</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>test.edge99.net</t>
+          <t>ti-api.edge99.net</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>100.86.174.68</t>
+          <t>100.72.29.57</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:09.391479Z</t>
+          <t>2026-01-09T16:24:14.072106Z</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6125,12 +6125,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>edbcd182eae447bdcb79d230631a2a7c</t>
+          <t>e4464c749341e0cc2c2036b93bd7f600</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ti-api.edge99.net</t>
+          <t>traefik.edge99.net</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>100.72.29.57</t>
+          <t>100.116.237.108</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-01-09T16:24:14.072106Z</t>
+          <t>2026-01-17T09:16:10.204614Z</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6185,22 +6185,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>e4464c749341e0cc2c2036b93bd7f600</t>
+          <t>5437b024aff99b20174f07f03e75053f</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>traefik.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>100.116.237.108</t>
+          <t>0 issuewild "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6230,22 +6230,26 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-01-17T09:16:10.204614Z</t>
+          <t>2025-12-26T23:53:32.288215Z</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5437b024aff99b20174f07f03e75053f</t>
+          <t>27643163ea8521f079bd5b3d546005fb</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6260,7 +6264,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0 issuewild "letsencrypt.org"</t>
+          <t>0 issue "letsencrypt.org"</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6290,18 +6294,18 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:32.288215Z</t>
+          <t>2025-12-26T23:53:31.459246Z</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>{'flags': 0, 'tag': 'issuewild', 'value': 'letsencrypt.org'}</t>
+          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -6309,26 +6313,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27643163ea8521f079bd5b3d546005fb</t>
+          <t>5ec54ecccbfab0e816a744473715792a</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>api.edge99.net</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0 issue "letsencrypt.org"</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
@@ -6338,7 +6342,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6354,31 +6358,27 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2025-12-26T23:53:58.741695Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:31.459246Z</t>
+          <t>2026-01-02T16:11:30.234893Z</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>{'flags': 0, 'tag': 'issue', 'value': 'letsencrypt.org'}</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5ec54ecccbfab0e816a744473715792a</t>
+          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>api.edge99.net</t>
+          <t>mt89.edge99.net</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.741695Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-01-02T16:11:30.234893Z</t>
+          <t>2026-02-23T09:20:49.817371Z</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6433,12 +6433,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>efba2d524819b2ec5c5d5ee995f47ed6</t>
+          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>mt89.edge99.net</t>
+          <t>mt-link.edge99.net</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:49.817371Z</t>
+          <t>2026-02-23T09:20:48.959702Z</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6493,12 +6493,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bc3b9c30ef0fd9829710ccbcf12bd74c</t>
+          <t>3f73002f0053f30885577d0827b3ba0f</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>mt-link.edge99.net</t>
+          <t>rwmt1._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:48.959702Z</t>
+          <t>2026-02-23T09:20:40.345035Z</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6553,12 +6553,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3f73002f0053f30885577d0827b3ba0f</t>
+          <t>3a44fa70856ae275d73da486bc402e96</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.edge99.net</t>
+          <t>rwmt2._domainkey.edge99.net</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.345035Z</t>
+          <t>2026-02-23T09:20:40.95412Z</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -6613,12 +6613,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3a44fa70856ae275d73da486bc402e96</t>
+          <t>7977c50b97c224d7845ce348cc7a170b</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.edge99.net</t>
+          <t>status.edge99.net</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>edge-mtl.edge99.net</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-02-23T09:20:40.95412Z</t>
+          <t>2026-01-05T11:23:19.93223Z</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6673,12 +6673,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7977c50b97c224d7845ce348cc7a170b</t>
+          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>status.edge99.net</t>
+          <t>www.edge99.net</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>edge-mtl.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-01-05T11:23:19.93223Z</t>
+          <t>2025-12-26T23:53:58.059446Z</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6733,36 +6733,36 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>b30deaebfaea39ca53c881f78bc76ed1</t>
+          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>www.edge99.net</t>
+          <t>_acme-challenge.edge99.net</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
         </is>
       </c>
       <c r="E105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:58.059446Z</t>
+          <t>2026-03-29T17:41:13.177706Z</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6793,12 +6793,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1b6fdf2a3c08989b9bf929449193dca0</t>
+          <t>50165c9904db7c779f07b98e9f943b47</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>_acme-challenge.edge99.net</t>
+          <t>_dmarc.edge99.net</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>IcouZ6dYLaD86rXg5YlVT6l_DoF8vjmm3F9AzZfLQv0</t>
+          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-03-29T17:41:13.177706Z</t>
+          <t>2025-12-26T23:53:33.496711Z</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -6853,12 +6853,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>50165c9904db7c779f07b98e9f943b47</t>
+          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>_dmarc.edge99.net</t>
+          <t>edge99.net</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:security@edge99.net</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:33.496711Z</t>
+          <t>2025-12-26T23:53:30.479433Z</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -6913,32 +6913,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a16c9eb9ef09553088c65e46bbd67fcc</t>
+          <t>77c251b8488617268d91ee1ebd51ede5</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>edge99.net</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>207.180.193.100</t>
         </is>
       </c>
       <c r="E108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2021-07-23T08:58:49.378112Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2025-12-26T23:53:30.479433Z</t>
+          <t>2021-07-23T12:56:39.987386Z</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -6973,12 +6973,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>77c251b8488617268d91ee1ebd51ede5</t>
+          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>listen.free-tekno.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>207.180.193.100</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2021-07-23T08:58:49.378112Z</t>
+          <t>2022-02-07T20:32:13.606665Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2021-07-23T12:56:39.987386Z</t>
+          <t>2022-02-07T20:32:43.921656Z</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dd673c4571ae6ec6ea4517da4047fa5f</t>
+          <t>de47139d99158674daebfa2bcc46381b</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>listen.free-tekno.com</t>
+          <t>radio.free-tekno.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>161.97.120.130</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:13.606665Z</t>
+          <t>2021-06-27T11:17:21.364442Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2022-02-07T20:32:43.921656Z</t>
+          <t>2022-02-16T15:58:36.261027Z</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -7093,12 +7093,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>de47139d99158674daebfa2bcc46381b</t>
+          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>radio.free-tekno.com</t>
+          <t>www.free-tekno.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2021-06-27T11:17:21.364442Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2022-02-16T15:58:36.261027Z</t>
+          <t>2022-02-07T16:41:14.791288Z</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7153,22 +7153,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5acccdfb3c59cd49cacd28e83e48d221</t>
+          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>www.free-tekno.com</t>
+          <t>mp3.free-tekno.com</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>161.97.120.130</t>
+          <t>freetekno.free.nf</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2022-02-07T16:41:14.791288Z</t>
+          <t>2023-07-04T19:53:02.363162Z</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7213,36 +7213,36 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ac7c113f029bd912a9b6fe78dffe02a5</t>
+          <t>9450bd2c3778824d44882bf3a36c136a</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>mp3.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>freetekno.free.nf</t>
+          <t>poste.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7258,37 +7258,39 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2023-07-04T19:53:02.363162Z</t>
+          <t>2022-02-16T15:14:24.531147Z</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9450bd2c3778824d44882bf3a36c136a</t>
+          <t>ec58d36579ccf292f4a659648d6a9c19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>_dmarc.free-tekno.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>poste.rivoluzioneinformatica.org</t>
+          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7318,29 +7320,27 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2022-02-16T15:14:24.531147Z</t>
+          <t>2022-02-16T15:36:47.274766Z</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="n">
-        <v>10</v>
-      </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ec58d36579ccf292f4a659648d6a9c19</t>
+          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>_dmarc.free-tekno.com</t>
+          <t>free-tekno.com</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; rua=mailto:cloud@free-tekno.com;</t>
+          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T12:57:13.550913Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2022-02-16T15:36:47.274766Z</t>
+          <t>2022-02-16T15:47:18.346287Z</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7395,7 +7395,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>f82cb05f0c7bd0ee554dc7a7e68481c2</t>
+          <t>15a4efde5824a7f870270570f044bf6a</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>v=spf1 mx ip4:161.97.120.130/32 a:mail.rivoluzioneinformatica.org a:poste.rivoluzioneinformatica.org -all</t>
+          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2022-02-16T12:57:13.550913Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2022-02-16T15:47:18.346287Z</t>
+          <t>2021-07-25T02:01:05.324193Z</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7455,12 +7455,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15a4efde5824a7f870270570f044bf6a</t>
+          <t>6f78e130390aca374862016649566194</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>free-tekno.com</t>
+          <t>s20220216247._domainkey.free-tekno.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>google-site-verification=u1RtWKENUcJYrh_iqqGrIQMTts0ipS2LpFZjtt7T-Nk</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2021-07-25T02:01:05.324193Z</t>
+          <t>2022-02-16T12:55:09.214302Z</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7515,36 +7515,36 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6f78e130390aca374862016649566194</t>
+          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>s20220216247._domainkey.free-tekno.com</t>
+          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA25fjdBEzCOeoRC5460U3HHjYEIjqtI4wkAVXidP5ynP9anEQ5i2+bW/lKh+xa5WKGjPofy/qxsnjuLE40ZnivPy7wfOwU3uOFf4CD5cen08xi/76vrqj3r1F29j8v+jJqB9+Z5RCOxCuu0Zx99okko+BaBej+O9W4Eh70d4PAb1TwrwNoBD47GnSLG3xu2b1NuXyWbuAEoQQ43/1+M689TJt7azAmG3yqft4J/7Oo0B7Wyk5V8Al2bpt6GYEoSV48HPrUC+MudIxgxVtR3O5oIVq9tHm7+jg5EY0GZpyk6yVJFlAXFJzt0OIKe4KvCngW0vHQSISmy0tgmZ8j38+uQIDAQAB</t>
+          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2022-02-16T12:55:09.214302Z</t>
+          <t>2022-12-10T19:31:31.948543Z</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7575,12 +7575,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>54e5f74cd09ee8a8c9729c9cdb0397b6</t>
+          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>freesounds-selfhosted.freeundergroundtekno.org</t>
+          <t>mp3.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>54a3646c-9701-4a8b-b6b0-e8b9f08e297f.cfargotunnel.com</t>
+          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2022-12-10T19:31:31.948543Z</t>
+          <t>2022-12-10T20:18:13.753251Z</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7635,12 +7635,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>f2d988c340f9edd8b38f1dcd778bb88a</t>
+          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>mp3.freeundergroundtekno.org</t>
+          <t>radio.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>7544e2f1-de2b-411b-9eed-4a6c28bf46ac.cfargotunnel.com</t>
+          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2022-12-10T20:18:13.753251Z</t>
+          <t>2024-06-08T18:04:10.985475Z</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7695,36 +7695,36 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7d449cbba90883fa8a14389f9a18a7a6</t>
+          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>radio.freeundergroundtekno.org</t>
+          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1e58dbc4-7d4f-4d5c-bf27-f801381a4fce.cfargotunnel.com</t>
+          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
         </is>
       </c>
       <c r="E121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2024-06-08T18:04:10.985475Z</t>
+          <t>2018-08-07T16:10:03.300043Z</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7755,12 +7755,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>b24f98873ca6f73f11bb06015e03a3d1</t>
+          <t>e302bd7fb84138a3a709507e25855226</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>_acme-challenge.sound.freeundergroundtekno.org</t>
+          <t>freeundergroundtekno.org</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4bHK_Yi224RlQPT3GaNFHfWNtm2reTuFAJitGpMFgM8</t>
+          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>120</v>
+        <v>3600</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7800,12 +7800,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2018-08-07T16:10:03.300043Z</t>
+          <t>2024-03-25T22:28:21.998451Z</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7815,22 +7815,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>e302bd7fb84138a3a709507e25855226</t>
+          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>freeundergroundtekno.org</t>
+          <t>api.gpfree.org</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>google-site-verification=UoPqDBPRj-_7eqBxrBhGViVVv41rzy51Zb_ZCmftsq0</t>
+          <t>100.98.112.23</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2024-03-25T22:28:21.998451Z</t>
+          <t>2026-02-20T08:59:49.153859Z</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -7875,12 +7875,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>edbbb21aeca4bf8ac037fabbcbeb403a</t>
+          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>api.gpfree.org</t>
+          <t>fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-02-20T08:59:49.153859Z</t>
+          <t>2026-03-18T15:05:00.060864Z</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -7935,12 +7935,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>d49d2505c54a34c8d0eaf609450cbac3</t>
+          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>fabgpt.gpfree.org</t>
+          <t>staging.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-03-18T15:05:00.060864Z</t>
+          <t>2026-03-18T15:10:56.641008Z</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -7995,12 +7995,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>e99f0b8d3a12de61ff7d1730f6ad3fac</t>
+          <t>2595a127a68f984ca81d16e940bd2e2d</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>staging.fabgpt.gpfree.org</t>
+          <t>wp.fabgpt.gpfree.org</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:56.641008Z</t>
+          <t>2026-03-18T15:10:57.310013Z</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -8055,22 +8055,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2595a127a68f984ca81d16e940bd2e2d</t>
+          <t>6df38438ed98575475bb7af5da9b052f</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>wp.fabgpt.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>100.98.112.23</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -8100,22 +8100,24 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-03-18T15:10:57.310013Z</t>
+          <t>2026-03-17T08:01:10.699402Z</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6df38438ed98575475bb7af5da9b052f</t>
+          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8130,7 +8132,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -8160,24 +8162,24 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.699402Z</t>
+          <t>2026-03-17T08:01:10.692178Z</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>f64d87e376a39c1368fe6b9b90cd0878</t>
+          <t>275da995ff6365d00940949c3be096b7</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8192,7 +8194,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -8222,39 +8224,39 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.692178Z</t>
+          <t>2026-03-17T08:01:10.680447Z</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>275da995ff6365d00940949c3be096b7</t>
+          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>_acme-challenge.test.gpfree.org</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -8264,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8273,7 +8275,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -8284,29 +8286,27 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.680447Z</t>
+          <t>2026-02-21T07:38:57.479193Z</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="n">
-        <v>84</v>
-      </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1e6f56fe27885e57eb13a67f8a68d1d6</t>
+          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>_acme-challenge.test.gpfree.org</t>
+          <t>cf2024-1._domainkey.gpfree.org</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>k_0Xb4ijdiRHwHmDqa0RR4hPf3IGxCpiG5WEQ1yxvB4</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-02-21T07:38:57.479193Z</t>
+          <t>2026-03-17T08:01:10.715552Z</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8361,12 +8361,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ff1e8a2b3b519ad9d2de65b8ae8e3b55</t>
+          <t>71dad7b6a76441275f93940f5f584af7</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.gpfree.org</t>
+          <t>_dmarc.gpfree.org</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.715552Z</t>
+          <t>2026-03-18T22:57:53.210752Z</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8421,12 +8421,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>71dad7b6a76441275f93940f5f584af7</t>
+          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>_dmarc.gpfree.org</t>
+          <t>gpfree.org</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:afb2208a49064786b1617b79c046dd42@dmarc-reports.cloudflare.net"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8466,12 +8466,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-03-18T22:57:53.210752Z</t>
+          <t>2026-03-17T08:01:10.707662Z</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8481,36 +8481,36 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2af0ef773ef2ff3152c24f73ac22bf8f</t>
+          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>gpfree.org</t>
+          <t>ai.irrazionale.org</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>1</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-03-17T08:01:10.707662Z</t>
+          <t>2025-03-21T11:57:02.473035Z</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8541,12 +8541,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3d0c18afd78dff56ae887d0b7f971bf0</t>
+          <t>737420529070901f1b0cd444ebf396fd</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ai.irrazionale.org</t>
+          <t>baserow.irrazionale.org</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>fc418fe6-ca4c-4b2d-988b-b2b9bddc570f.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-03-21T11:57:02.473035Z</t>
+          <t>2025-02-07T16:23:37.038965Z</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>737420529070901f1b0cd444ebf396fd</t>
+          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>baserow.irrazionale.org</t>
+          <t>check.irrazionale.org</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-02-07T16:23:37.038965Z</t>
+          <t>2025-04-10T17:26:36.959974Z</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8661,12 +8661,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2628b62f7c721d0e34d5ad5f81f94aa6</t>
+          <t>081907c20660bf785f8a99b15f7ae6fa</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>check.irrazionale.org</t>
+          <t>cloud.irrazionale.org</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>eb879ac1-3924-4f69-9c6c-75f6a9e1cdb8.cfargotunnel.com</t>
+          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2025-04-10T17:26:36.959974Z</t>
+          <t>2022-12-11T16:25:07.205868Z</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8721,12 +8721,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>081907c20660bf785f8a99b15f7ae6fa</t>
+          <t>d0e96bb2faf9ed17182c357e39b68779</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>cloud.irrazionale.org</t>
+          <t>coolify.irrazionale.org</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>379e723b-0e63-4ee0-aabe-5009125009c9.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2022-12-11T16:25:07.205868Z</t>
+          <t>2025-02-09T22:15:14.34368Z</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8781,12 +8781,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>d0e96bb2faf9ed17182c357e39b68779</t>
+          <t>911a85c4a4a11c6e7c594788937a2456</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>coolify.irrazionale.org</t>
+          <t>dell.irrazionale.org</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-02-09T22:15:14.34368Z</t>
+          <t>2023-12-01T12:39:10.88625Z</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -8841,12 +8841,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>911a85c4a4a11c6e7c594788937a2456</t>
+          <t>60d0a2d1367b6b64c398aa37848efae3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>dell.irrazionale.org</t>
+          <t>docker.irrazionale.org</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4e789f43-bcab-410e-a7c8-9c7bd88fd294.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2023-12-01T12:39:10.88625Z</t>
+          <t>2025-02-07T16:29:08.840612Z</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>60d0a2d1367b6b64c398aa37848efae3</t>
+          <t>08d407943ed4067865b5a819494093df</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>docker.irrazionale.org</t>
+          <t>freesounds.irrazionale.org</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2025-02-07T16:29:08.840612Z</t>
+          <t>2022-05-29T10:34:39.700377Z</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -8961,12 +8961,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>08d407943ed4067865b5a819494093df</t>
+          <t>41be2e667e4654c8425c3747809eaf4b</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>freesounds.irrazionale.org</t>
+          <t>git.irrazionale.org</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>86cfa504-c90d-46fd-a7f9-8c8d7a74ec1b.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2022-05-29T10:34:39.700377Z</t>
+          <t>2025-02-09T17:43:27.673327Z</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -9021,12 +9021,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>41be2e667e4654c8425c3747809eaf4b</t>
+          <t>216f28a4197e4846265257d9a19df44a</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>git.irrazionale.org</t>
+          <t>jellyfin.irrazionale.org</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2025-02-09T17:43:27.673327Z</t>
+          <t>2023-12-01T16:34:33.145093Z</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -9081,12 +9081,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>216f28a4197e4846265257d9a19df44a</t>
+          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jellyfin.irrazionale.org</t>
+          <t>lf.irrazionale.org</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ecb8d351-a34c-4b72-829d-9e0ef5726b65.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2023-12-01T16:34:33.145093Z</t>
+          <t>2024-04-25T08:35:09.947241Z</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -9141,12 +9141,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>a294caebd6eeaa83278ae5e170afa4a7</t>
+          <t>b3c12f8816422fb6e017703c896aa4eb</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>lf.irrazionale.org</t>
+          <t>localhost.irrazionale.org</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2024-04-25T08:35:09.947241Z</t>
+          <t>2025-03-26T09:51:19.730468Z</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9201,12 +9201,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>b3c12f8816422fb6e017703c896aa4eb</t>
+          <t>59f655ac3982f7c3d6318c237aada804</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>localhost.irrazionale.org</t>
+          <t>mixpost.irrazionale.org</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>05dcfc0e-c6f7-45c8-9c51-04d3ea300b3c.cfargotunnel.com</t>
+          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2025-03-26T09:51:19.730468Z</t>
+          <t>2025-06-25T19:29:40.179134Z</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9261,12 +9261,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>59f655ac3982f7c3d6318c237aada804</t>
+          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mixpost.irrazionale.org</t>
+          <t>mt-link.irrazionale.org</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>07122097-0310-42ba-b8c6-ea15e3b8612e.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E147" t="b">
         <v>1</v>
       </c>
       <c r="F147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -9306,12 +9306,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2025-06-25T19:29:40.179134Z</t>
+          <t>2023-07-06T15:34:57.894134Z</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9321,12 +9321,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>f4dca49d67d59d15ae0d95d59da4e1bc</t>
+          <t>3d3ea0a30645f9869829e88faee2503f</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>mt-link.irrazionale.org</t>
+          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:57.894134Z</t>
+          <t>2023-07-06T15:33:25.6031Z</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9381,12 +9381,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3d3ea0a30645f9869829e88faee2503f</t>
+          <t>1229fb10c393330dc3c65ae010d33165</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>mtvcz748l8xjyyn1.irrazionale.org</t>
+          <t>ocr.irrazionale.org</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9396,14 +9396,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E149" t="b">
         <v>1</v>
       </c>
       <c r="F149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:25.6031Z</t>
+          <t>2025-04-14T16:13:52.683863Z</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9441,12 +9441,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1229fb10c393330dc3c65ae010d33165</t>
+          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ocr.irrazionale.org</t>
+          <t>ollama.irrazionale.org</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2025-04-14T16:13:52.683863Z</t>
+          <t>2024-04-20T14:38:22.706136Z</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9501,12 +9501,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>0f265f5f7fc8993d0ab2639cf54dd5da</t>
+          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ollama.irrazionale.org</t>
+          <t>pdf2docx.irrazionale.org</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>98741367-c2d6-4791-adc2-f20eee96e6c3.cfargotunnel.com</t>
+          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2024-04-20T14:38:22.706136Z</t>
+          <t>2025-04-14T15:30:12.902487Z</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9561,12 +9561,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>78c3a51bff323b9cf5c78e4d2c699452</t>
+          <t>7131e78a346aea946d969f014c2cb1e9</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>pdf2docx.irrazionale.org</t>
+          <t>postiz.irrazionale.org</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>bc9f57f2-e22f-4154-a26b-a765f0942d61.cfargotunnel.com</t>
+          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-04-14T15:30:12.902487Z</t>
+          <t>2025-06-25T07:43:38.264549Z</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9621,12 +9621,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7131e78a346aea946d969f014c2cb1e9</t>
+          <t>4a64c597d17da513e052355df93bbc58</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>postiz.irrazionale.org</t>
+          <t>powerdns.irrazionale.org</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>8212a2e4-846e-4096-bd97-3349c9da4269.cfargotunnel.com</t>
+          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2025-06-25T07:43:38.264549Z</t>
+          <t>2022-07-28T21:04:04.261466Z</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9681,12 +9681,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4a64c597d17da513e052355df93bbc58</t>
+          <t>4bd65cc8d342c16851d7e90462f78579</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>powerdns.irrazionale.org</t>
+          <t>proxmox.irrazionale.org</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>5aa9a43c-0d36-4ba4-aeae-bbd15b710672.cfargotunnel.com</t>
+          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2022-07-28T21:04:04.261466Z</t>
+          <t>2025-02-07T16:35:38.19329Z</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -9741,12 +9741,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4bd65cc8d342c16851d7e90462f78579</t>
+          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>proxmox.irrazionale.org</t>
+          <t>proxmox-ssh.irrazionale.org</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2025-02-07T16:35:38.19329Z</t>
+          <t>2025-02-07T16:36:02.480326Z</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -9801,12 +9801,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>bcecbb8389554f8c10dcbe5342f07c71</t>
+          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>proxmox-ssh.irrazionale.org</t>
+          <t>rwmt1._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9816,14 +9816,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>b07e1b74-56b3-479f-a59f-ee5c153f9ad5.cfargotunnel.com</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E156" t="b">
         <v>1</v>
       </c>
       <c r="F156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2025-02-07T16:36:02.480326Z</t>
+          <t>2023-07-06T15:34:03.879259Z</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -9861,12 +9861,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4df15e68dd88bfa0ecd696b2dd67008e</t>
+          <t>04d14cb456a1976f403ee148eca05cc8</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.irrazionale.org</t>
+          <t>rwmt2._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:03.879259Z</t>
+          <t>2023-07-06T15:34:18.717224Z</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -9921,12 +9921,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>04d14cb456a1976f403ee148eca05cc8</t>
+          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.irrazionale.org</t>
+          <t>s3.irrazionale.org</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9936,14 +9936,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E158" t="b">
         <v>1</v>
       </c>
       <c r="F158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:18.717224Z</t>
+          <t>2025-02-07T16:30:35.386852Z</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -9981,12 +9981,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8ee0fa4fe49caa8b43660be5e1d1c512</t>
+          <t>0ce0da84393eb2e44a959deb2116cce5</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>s3.irrazionale.org</t>
+          <t>s3ui.irrazionale.org</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:35.386852Z</t>
+          <t>2025-02-07T16:30:54.891274Z</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -10041,12 +10041,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>0ce0da84393eb2e44a959deb2116cce5</t>
+          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>s3ui.irrazionale.org</t>
+          <t>sci-fi.irrazionale.org</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-02-07T16:30:54.891274Z</t>
+          <t>2025-03-26T09:46:23.862818Z</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -10101,12 +10101,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5a8bf821d63cc1869542ffd4dac042ef</t>
+          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>sci-fi.irrazionale.org</t>
+          <t>search.irrazionale.org</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20dc8c4c-6a80-4cc7-be33-cc9e43dbea4c.cfargotunnel.com</t>
+          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -10146,12 +10146,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2025-03-26T09:46:23.862818Z</t>
+          <t>2025-02-09T15:52:15.13208Z</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -10161,12 +10161,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>f1d8eb95f42108e4b07e86388c8670e7</t>
+          <t>d136067486f9bfd1260a66e04c217624</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>search.irrazionale.org</t>
+          <t>webcheck.irrazionale.org</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2025-02-09T15:52:15.13208Z</t>
+          <t>2025-02-07T16:26:34.171441Z</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -10221,36 +10221,36 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>d136067486f9bfd1260a66e04c217624</t>
+          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>webcheck.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6bc1493d-6cb7-451c-b848-53c8a2043e65.cfargotunnel.com</t>
+          <t>mail.irrazionale.org</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10266,22 +10266,24 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2025-02-07T16:26:34.171441Z</t>
+          <t>2022-07-15T07:14:33.759478Z</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>095deb0b6f4f0327cf9d1e1abc53e523</t>
+          <t>5e61f46e73d33d23b901c830c11d05e5</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10296,7 +10298,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>mail.irrazionale.org</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -10326,24 +10328,24 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2022-07-15T07:14:33.759478Z</t>
+          <t>2022-03-21T23:21:47.93845Z</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5e61f46e73d33d23b901c830c11d05e5</t>
+          <t>4a187b659dadf78253cb30054350314c</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10358,7 +10360,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>route2mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -10388,24 +10390,24 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:47.93845Z</t>
+          <t>2022-03-21T23:21:36.591334Z</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4a187b659dadf78253cb30054350314c</t>
+          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10420,7 +10422,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>route2mx.cloudflare.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -10450,39 +10452,39 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:36.591334Z</t>
+          <t>2022-03-21T23:21:22.978524Z</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8f14619268c7a453f27c0cc292f5bdf6</t>
+          <t>bb6fca1069dfef36eac3160ec423215a</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>safe.irrazionale.org</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>dnsafe.irrazionale.org</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -10512,39 +10514,37 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2022-03-21T23:21:22.978524Z</t>
+          <t>2022-03-25T12:14:53.694611Z</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="n">
-        <v>89</v>
-      </c>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>bb6fca1069dfef36eac3160ec423215a</t>
+          <t>3a04124b47167ef39224aa1b60a8fe25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>safe.irrazionale.org</t>
+          <t>_acme-challenge.mail.irrazionale.org</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>dnsafe.irrazionale.org</t>
+          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -10554,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2022-03-25T12:14:53.694611Z</t>
+          <t>2022-05-17T14:04:00.295343Z</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -10589,12 +10589,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3a04124b47167ef39224aa1b60a8fe25</t>
+          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>_acme-challenge.mail.irrazionale.org</t>
+          <t>_dmarc.irrazionale.org</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>UqWxLrUNf7_wrvKMrtVQqMz-Nl_UtRVF6pbE8tsHdzE</t>
+          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -10614,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2022-05-17T14:04:00.295343Z</t>
+          <t>2024-04-17T09:09:11.011539Z</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -10649,7 +10649,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1d8156b40d6aacadc2dbd965cdddf5a2</t>
+          <t>c931695adebdf9cc13b66924f8d442a2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:rua@dmarc.brevo.com</t>
+          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2024-04-17T09:09:11.011539Z</t>
+          <t>2023-07-06T15:34:35.980156Z</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -10709,7 +10709,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>c931695adebdf9cc13b66924f8d442a2</t>
+          <t>5674a44427225f44209d188901e7e212</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=none; rua=mailto:dmarc@smtp.mailtrap.live; ruf=mailto:dmarc@smtp.mailtrap.live; rf=afrf; pct=100</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2023-07-06T15:34:35.980156Z</t>
+          <t>2022-07-15T07:15:44.35849Z</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
@@ -10769,12 +10769,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5674a44427225f44209d188901e7e212</t>
+          <t>575daba57b52a33ae44441e93e44ad93</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>_dmarc.irrazionale.org</t>
+          <t>irrazionale.org</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2022-07-15T07:15:44.35849Z</t>
+          <t>2024-04-17T09:08:34.680551Z</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -10829,7 +10829,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>575daba57b52a33ae44441e93e44ad93</t>
+          <t>8ae5f18920790fbc1ac6e57676db376b</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>brevo-code:6f4f7efb6520b5418b28b67f298c9b52</t>
+          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:34.680551Z</t>
+          <t>2023-07-06T15:33:42.660644Z</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -10889,7 +10889,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8ae5f18920790fbc1ac6e57676db376b</t>
+          <t>5f752add42e06a88468c1b1203a5241c</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 include:_spf.smtp.mailtrap.live -all</t>
+          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2023-07-06T15:33:42.660644Z</t>
+          <t>2023-06-12T10:59:14.29918Z</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -10949,7 +10949,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5f752add42e06a88468c1b1203a5241c</t>
+          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>zone-ownership-verification-58c91853bd399630f635536dca469de68c690b6a4b62aa2e95ceecc9de895f73</t>
+          <t>v=spf1 ip4:185.182.185.194 -all</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2023-06-12T10:59:14.29918Z</t>
+          <t>2022-07-15T07:16:37.604542Z</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -11009,12 +11009,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>0f26a20e5f4dd405e38ae5978d278e3d</t>
+          <t>96bf76d43d32043fc586f04d28efe912</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>irrazionale.org</t>
+          <t>mail._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>v=spf1 ip4:185.182.185.194 -all</t>
+          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2022-07-15T07:16:37.604542Z</t>
+          <t>2024-04-17T09:08:52.915406Z</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
@@ -11069,12 +11069,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>96bf76d43d32043fc586f04d28efe912</t>
+          <t>6aa7d6d1576b8790519602102e390beb</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>mail._domainkey.irrazionale.org</t>
+          <t>s20220715915._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>k=rsa;p=MIGfMA0GCSqGSIb3DQEBAQUAA4GNADCBiQKBgQDeMVIzrCa3T14JsNY0IRv5/2V1/v2itlviLQBwXsa7shBD6TrBkswsFUToPyMRWC9tbR/5ey0nRBH0ZVxp+lsmTxid2Y2z+FApQ6ra2VsXfbJP3HE6wAO0YTVEJt1TmeczhEd2Jiz/fcabIISgXEdSpTYJhb0ct0VJRxcg4c8c7wIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2024-04-17T09:08:52.915406Z</t>
+          <t>2022-07-15T07:12:54.583273Z</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -11129,12 +11129,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6aa7d6d1576b8790519602102e390beb</t>
+          <t>f07372fefe2aeec92ba78a42ee921960</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>s20220715915._domainkey.irrazionale.org</t>
+          <t>s20221212161._domainkey.irrazionale.org</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAyNn2hzqOisuAb2kxl2iqzi7+latoU5BIcqzoLq2IF5PSw8F/ThnpADmyJEoBqDjvPyFpsJAor3lVVE9hE0PnJkDoKmVGyrFTWQxdZr0bUEJd6Tv/3+0yqBxyV4r6t0x6HuUIFERXl2tXBCog5asMqOoYlFjUSagQV7T8r00essEI8KFvMYRE9ec9CumhoosbtHHYZ3mX/HwL6CEZKi3glJymgoxl3W9AeINn+93qsSzIAekLaTEmnlKbrLWBcyhLPR/20xSSaUOJslfn7ucV8OabomN44BJi3lWxQvoHoM6BLHhs48k8jOzROLn/Svdv51TuM25xPuyAKfapJpZEIQIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-07-15T07:12:54.583273Z</t>
+          <t>2022-12-12T15:43:59.509606Z</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -11189,22 +11189,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>f07372fefe2aeec92ba78a42ee921960</t>
+          <t>f02f658bd3f849218f8880600ee8f124</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>s20221212161._domainkey.irrazionale.org</t>
+          <t>proxmox-dc2-mn.italiacdn.net</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAofbiDgrsqmp59MqGRDqdglbPZnE5MfHcQxLrCU/3szYwS5JfZBBqS/HMvejGoVlgb3uH+CHuSdGgu8gQzuDob8ULjskAQA93FFpob8MvygixtZQITuiAFl6W4nFzebxN2Tg6zO9oS+eeGQsqq95jp2YWLjlvYcpw2dZU0sdmGJw3VlUrPqJh4+Qp8P5vvGhYHiPykVuZSqd91TqX7OuEzpOabt2uas32ea0AquzzUgpbjbxv7GJdCdccmD5tYBW7Sm6VcWvPXSo42N2gYMQ5R+24tN3QViBOcbBUgX+1K91d2Yad3GqTttoJZ7mt4oiR/t15BcavS9yzutzCeR7b2QIDAQAB</t>
+          <t>100.92.242.58</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2022-12-12T15:43:59.509606Z</t>
+          <t>2025-03-19T12:53:01.306549Z</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11249,36 +11249,36 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>f02f658bd3f849218f8880600ee8f124</t>
+          <t>25f1985f805e21184de23f5dd6f43ea9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>proxmox-dc2-mn.italiacdn.net</t>
+          <t>bin.italiacdn.net</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>100.92.242.58</t>
+          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-03-19T12:53:01.306549Z</t>
+          <t>2025-03-18T20:26:37.20432Z</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11309,12 +11309,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>25f1985f805e21184de23f5dd6f43ea9</t>
+          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>bin.italiacdn.net</t>
+          <t>logs.italiacdn.net</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>62012bb4-9a36-4017-b533-489f1e455049.cfargotunnel.com</t>
+          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.20432Z</t>
+          <t>2025-03-18T23:39:26.579932Z</t>
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
@@ -11369,12 +11369,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>35b29e9d5ed68e0541ae38a785efe1ce</t>
+          <t>b013512ac14813f9241bfb82d58e6a15</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>logs.italiacdn.net</t>
+          <t>private.italiacdn.net</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>00f31d96-6439-42a2-b318-a67a0c4a3185.cfargotunnel.com</t>
+          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -11414,12 +11414,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-03-18T23:39:26.579932Z</t>
+          <t>2025-03-19T10:27:09.22597Z</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -11429,12 +11429,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>b013512ac14813f9241bfb82d58e6a15</t>
+          <t>da6f732331d53062b4a64822c4d8053c</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>private.italiacdn.net</t>
+          <t>public-bucket.italiacdn.net</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1f087ba6-ed46-46e1-ad14-5c6de5a6cb17.cfargotunnel.com</t>
+          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2025-03-19T10:27:09.22597Z</t>
+          <t>2025-03-21T20:12:10.177478Z</t>
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
@@ -11489,12 +11489,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>da6f732331d53062b4a64822c4d8053c</t>
+          <t>68ff9d51859905c9e8f951acf9650166</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>public-bucket.italiacdn.net</t>
+          <t>vault.italiacdn.net</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>5765bae3-e774-4f5e-bc6f-618607856ac4.cfargotunnel.com</t>
+          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2025-03-21T20:12:10.177478Z</t>
+          <t>2025-03-19T09:30:39.063935Z</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11549,12 +11549,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>68ff9d51859905c9e8f951acf9650166</t>
+          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vault.italiacdn.net</t>
+          <t>vpn.italiacdn.net</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>c59561f4-d014-47f6-8a62-39e616d1303a.cfargotunnel.com</t>
+          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2025-03-19T09:30:39.063935Z</t>
+          <t>2025-03-18T20:26:37.148167Z</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -11609,36 +11609,36 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3f675bb7dfbfea17e4c7b970c12c90c4</t>
+          <t>14efda500a1c1e9c12dffecc2640246d</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>vpn.italiacdn.net</t>
+          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>19ccacfd-5678-4b66-99ae-ee25848d03fe.cfargotunnel.com</t>
+          <t>27b4d1e9dabc5765ebb48532ae2443</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2025-03-18T20:26:37.148167Z</t>
+          <t>2025-03-19T10:11:55.275773Z</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -11669,22 +11669,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>14efda500a1c1e9c12dffecc2640246d</t>
+          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>_github-pages-challenge-italiacdn.italiacdn.net</t>
+          <t>aws.italiadns.net</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>27b4d1e9dabc5765ebb48532ae2443</t>
+          <t>ns-1683.awsdns-18.co.uk</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -11694,7 +11694,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2025-03-19T10:11:55.275773Z</t>
+          <t>2025-03-03T11:17:51.528649Z</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -11729,7 +11729,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>c0f4b4c2ad85a76c92a692cda9b07f2f</t>
+          <t>4131e3d65c1df20458045bfa612298e9</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ns-1683.awsdns-18.co.uk</t>
+          <t>ns-1303.awsdns-34.org</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:51.528649Z</t>
+          <t>2025-03-03T11:17:34.736768Z</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -11789,22 +11789,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4131e3d65c1df20458045bfa612298e9</t>
+          <t>03da4898b7afbb1408bfdd51f42e5936</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>aws.italiadns.net</t>
+          <t>kisstube.tv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ns-1303.awsdns-34.org</t>
+          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2025-03-03T11:17:34.736768Z</t>
+          <t>2015-05-25T23:39:18.201448Z</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -11849,7 +11849,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>03da4898b7afbb1408bfdd51f42e5936</t>
+          <t>fd06957f7e745e10c388665bb8be096a</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>google-site-verification=6DRoK-0kxVjTkrYzq-kCZy3nDRa1dBHfsCcbAzm1dYw</t>
+          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2015-05-25T23:39:18.201448Z</t>
+          <t>2014-06-23T19:34:28.649657Z</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -11909,7 +11909,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>fd06957f7e745e10c388665bb8be096a</t>
+          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>google-site-verification=39ep5VoK19J3GTzqrCZ3wKSPlg5bQXkFsuFQy0mtLeA</t>
+          <t>v=spf1 a mx ~all</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.649657Z</t>
+          <t>2014-06-23T19:34:28.647128Z</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -11969,36 +11969,36 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ccf7ca30f014519f55993c5bc5846c1a</t>
+          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>kisstube.tv</t>
+          <t>www.mixidaw.com</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>v=spf1 a mx ~all</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12014,12 +12014,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2026-04-03T12:16:43.381049Z</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2014-06-23T19:34:28.647128Z</t>
+          <t>2026-04-03T18:58:28.024399Z</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -12029,12 +12029,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>e10b8a0c9773b8442e86d295581b0fe5</t>
+          <t>b738ae8c910e28345612400cb8a6e23e</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>www.mixidaw.com</t>
+          <t>ssh.repolizer.com</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-04-03T12:16:43.381049Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-04-03T18:58:28.024399Z</t>
+          <t>2025-04-09T08:29:51.295021Z</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -12089,12 +12089,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>b738ae8c910e28345612400cb8a6e23e</t>
+          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ssh.repolizer.com</t>
+          <t>www.repolizer.com</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12134,12 +12134,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-04-23T08:30:24.446765Z</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2025-04-09T08:29:51.295021Z</t>
+          <t>2025-04-23T08:34:01.380912Z</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -12149,36 +12149,36 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>bfd43018c9b1cd41cc29efc4c62c6d8c</t>
+          <t>c7df12561d64e4e680c6b0859c123f99</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>www.repolizer.com</t>
+          <t>imap.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>a7a86777-918b-4a27-9ad1-ab108649b92d.cfargotunnel.com</t>
+          <t>185.182.185.194</t>
         </is>
       </c>
       <c r="E195" t="b">
         <v>1</v>
       </c>
       <c r="F195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>1</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2025-04-23T08:30:24.446765Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2025-04-23T08:34:01.380912Z</t>
+          <t>2022-05-22T11:08:51.308823Z</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -12209,12 +12209,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>c7df12561d64e4e680c6b0859c123f99</t>
+          <t>e95c85414a6c93e847a2755df7c16cf0</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>imap.rivoluzioneinformatica.org</t>
+          <t>mail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:51.308823Z</t>
+          <t>2022-05-22T10:15:04.05472Z</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
@@ -12269,12 +12269,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>e95c85414a6c93e847a2755df7c16cf0</t>
+          <t>6834f98896056a837138409566211327</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>mail.rivoluzioneinformatica.org</t>
+          <t>smtp.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12314,12 +12314,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2022-05-22T10:15:04.05472Z</t>
+          <t>2022-05-22T11:08:43.086179Z</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -12329,12 +12329,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6834f98896056a837138409566211327</t>
+          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>smtp.rivoluzioneinformatica.org</t>
+          <t>webmail.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12351,7 +12351,7 @@
         <v>1</v>
       </c>
       <c r="F198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2022-05-22T11:08:43.086179Z</t>
+          <t>2022-05-22T08:24:00.700773Z</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -12389,22 +12389,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ba18f2da24401c4bc0c2ed6444470ab3</t>
+          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>webmail.rivoluzioneinformatica.org</t>
+          <t>git.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>185.182.185.194</t>
+          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2022-05-22T08:24:00.700773Z</t>
+          <t>2025-01-29T00:26:34.637101Z</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -12449,12 +12449,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>37bbd8bcff79b84679e1be20a97fbd4f</t>
+          <t>eb220c9fb1df30719c788ef51fe312f6</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>git.rivoluzioneinformatica.org</t>
+          <t>npm.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>b98dd568-bdbf-415a-8894-f30bb5bbbf91.cfargotunnel.com</t>
+          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2025-01-29T00:26:34.637101Z</t>
+          <t>2022-02-09T11:43:38.114483Z</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -12509,12 +12509,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>eb220c9fb1df30719c788ef51fe312f6</t>
+          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>npm.rivoluzioneinformatica.org</t>
+          <t>proxmox.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>692501dc-d195-4f10-b0a7-11a71a4cef78.cfargotunnel.com</t>
+          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2022-02-09T11:43:38.114483Z</t>
+          <t>2022-12-12T15:18:23.651021Z</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -12569,12 +12569,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>9feadf111b5434fd8dd2b41f8008ca09</t>
+          <t>236f1b867d3720d5dd29c6af49782d62</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>proxmox.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4436d941-eff4-4134-91a8-c5400be27423.cfargotunnel.com</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2022-12-12T15:18:23.651021Z</t>
+          <t>2023-11-10T15:34:50.070177Z</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -12629,12 +12629,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>236f1b867d3720d5dd29c6af49782d62</t>
+          <t>7c6da25c8e1e486da458cd5373402382</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>vpn.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-11-10T15:34:50.070177Z</t>
+          <t>2023-02-11T13:51:31.288382Z</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
@@ -12689,12 +12689,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7c6da25c8e1e486da458cd5373402382</t>
+          <t>3045396196bc00b6e05726f94825c6bd</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>vpn.rivoluzioneinformatica.org</t>
+          <t>www.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-08-17T08:57:50.756388Z</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-02-11T13:51:31.288382Z</t>
+          <t>2022-08-17T08:59:41.92016Z</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -12749,12 +12749,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3045396196bc00b6e05726f94825c6bd</t>
+          <t>25f714bcbfe5ff8215c314a503379edc</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>www.rivoluzioneinformatica.org</t>
+          <t>xmq.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2022-08-17T08:57:50.756388Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2022-08-17T08:59:41.92016Z</t>
+          <t>2023-02-07T20:14:06.346543Z</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -12809,41 +12809,41 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>25f714bcbfe5ff8215c314a503379edc</t>
+          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>xmq.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>faa2f03f-72a7-4812-a2f9-18c9db40c328.cfargotunnel.com</t>
+          <t>amir.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -12854,22 +12854,24 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2023-02-07T20:14:06.346543Z</t>
+          <t>2023-06-12T11:01:48.035723Z</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
+      <c r="P206" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3a2fa8fe309047db5c79bf90a17c2580</t>
+          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12884,7 +12886,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>amir.mx.cloudflare.net</t>
+          <t>linda.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -12914,24 +12916,24 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.035723Z</t>
+          <t>2023-06-12T11:01:48.026902Z</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>177c0d9e3950bcc6a4ede7696aacb0a7</t>
+          <t>bcd73d5a0e03a2593be162cd5259a678</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12946,7 +12948,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>linda.mx.cloudflare.net</t>
+          <t>isaac.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -12976,39 +12978,39 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.026902Z</t>
+          <t>2023-06-12T11:01:48.018567Z</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>bcd73d5a0e03a2593be162cd5259a678</t>
+          <t>e6ffaf786ff743b47650f73557b07b66</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>isaac.mx.cloudflare.net</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -13038,29 +13040,27 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.018567Z</t>
+          <t>2025-03-13T15:24:01.244511Z</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="n">
-        <v>97</v>
-      </c>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>e6ffaf786ff743b47650f73557b07b66</t>
+          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.rivoluzioneinformatica.org</t>
+          <t>_dmarc.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -13100,12 +13100,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2022-02-07T15:43:39.763425Z</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2025-03-13T15:24:01.244511Z</t>
+          <t>2022-05-22T11:09:18.092063Z</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6bad42a7eedda28b7979d37d8e66d6d8</t>
+          <t>2a74f92cf716979d913217d640655261</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>_dmarc.rivoluzioneinformatica.org</t>
+          <t>rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; rua=mailto:weqc8axy@ag.eu.dmarcian.com</t>
+          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2022-02-07T15:43:39.763425Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2022-05-22T11:09:18.092063Z</t>
+          <t>2023-11-09T20:49:42.435335Z</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2a74f92cf716979d913217d640655261</t>
+          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>openai-domain-verification=dv-LwNd6wuOrll7KNwSnOzMAlPT</t>
+          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2023-11-09T20:49:42.435335Z</t>
+          <t>2023-06-12T11:01:48.044476Z</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>db8ada7f22832e3e4f352d5bd7829a4f</t>
+          <t>47bb0eec812c7e5f3961cb9079727d80</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>v=spf1 include:_spf.mx.cloudflare.net ~all</t>
+          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -13280,12 +13280,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2023-06-12T11:01:48.044476Z</t>
+          <t>2022-08-17T11:49:34.320428Z</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13295,12 +13295,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>47bb0eec812c7e5f3961cb9079727d80</t>
+          <t>9abd161d29cb47ce6cfa783657e67723</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>rivoluzioneinformatica.org</t>
+          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>google-site-verification=IjTuC9rcrlAzy_NPt27HTlWxytX_NsTAR_FnpyT3VZI</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -13340,12 +13340,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2022-05-13T21:13:25.301942Z</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2022-08-17T11:49:34.320428Z</t>
+          <t>2022-05-22T10:18:49.411362Z</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13355,12 +13355,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9abd161d29cb47ce6cfa783657e67723</t>
+          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>s20220522816._domainkey.rivoluzioneinformatica.org</t>
+          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAx3UfU+JrN8hQLHmMKQb4fVNTDP7rN7m0qzh0T/PV9xgHuuyckzIjqjG+elA1+Fn7Wo+DHFpGimlwVH2npG9Csbn2vAVcjydIsH17wqjqz0QSGoKoEXc3D0oTL4t2Lclz5gkRU/fo4578PmNZL6zPUZRwSGChTGNHG2R5I0W3HfIEYzULppN8DqsRbWxO/T5aGhhd+MMQt9gGMrNgW9BeeKQmOmIimuVozfLCW4rKLEREwOLYD75vhqTY0deCi3NnEXfap4Cqf7gI9F4MSXUoUiYBVRLqWSlDWH6uErQciiJZ8sw64fIZCQxpgYt9pXr5OOtThYiRWRrAXE5DTHEI1wIDAQAB</t>
+          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -13400,12 +13400,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2022-05-13T21:13:25.301942Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2022-05-22T10:18:49.411362Z</t>
+          <t>2022-12-12T15:42:56.669675Z</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13415,29 +13415,29 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>40834d23224c0eb0f3ae2f6cb80411fa</t>
+          <t>f24ad5153aa35ff9aa2dcbccf822051c</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>s20221212131._domainkey.rivoluzioneinformatica.org</t>
+          <t>txt2vst.com</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA0rb2uVzRTT2zZeqCpsJfX/nINuSJuyfV8CFWiDFXiQjrUHnVGg9dit2iQOVK+3opfQ+IG8OIAogmGWL4MUcqgLIF5t1mQKImdh/Ni1D7WGNpFvXNcohczpvMmGSVXOn9QY2sg+KmkSDO1qwS2WIuXQDxEGJ+iZVMMgMy37vtVyk3bw7bqOKgGEEC2pBpJU4E4tdA6gI8/ZLuBp4ejmT3ZKRS4Z2tyq91qAF9R+tRspMxSEMeI+OiBhYiB+wms2CvGCS8YtfC2mq7YwXfvTTg7eEdS6UU+0gCZWL0e8gl7edsY1wnZmM3lp+SY3WXbiONYy0/T96Xdg9kxCcr/1mBaQIDAQAB</t>
+          <t>192.0.2.1</t>
         </is>
       </c>
       <c r="E216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
         <v>1</v>
@@ -13452,7 +13452,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Created during Cloudflare Rules deployment process for page_rules</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13460,44 +13464,48 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
+          <t>2026-05-11T19:37:07.379818Z</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2022-12-12T15:42:56.669675Z</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
+          <t>2026-05-11T19:37:07.379818Z</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>2026-05-11T19:37:07.379818Z</t>
+        </is>
+      </c>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>6c874506c8ce87bd95aeb7af511402a4</t>
+          <t>614d74460e6074a1b082554768e4fb65</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.videodioggi.com</t>
+          <t>www.txt2vst.com</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>185.199.110.153</t>
         </is>
       </c>
       <c r="E217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>1</v>
@@ -13509,10 +13517,14 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr"/>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>GiiHub Pages</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13520,27 +13532,31 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
+          <t>2026-05-11T19:35:38.524857Z</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2025-03-14T01:50:15.254316Z</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
+          <t>2026-05-11T21:59:15.337255Z</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>2026-05-11T19:35:38.524857Z</t>
+        </is>
+      </c>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>d745f5935c526f8ec4c18455bb114e2c</t>
+          <t>6c874506c8ce87bd95aeb7af511402a4</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>_dmarc.videodioggi.com</t>
+          <t>cf2024-1._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13550,7 +13566,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -13569,7 +13585,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -13580,12 +13596,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.516418Z</t>
+          <t>2025-03-14T01:50:15.254316Z</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
@@ -13595,12 +13611,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>174e7c363d39762d0e764dca9d4f83fe</t>
+          <t>d745f5935c526f8ec4c18455bb114e2c</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>*._domainkey.videodioggi.com</t>
+          <t>_dmarc.videodioggi.com</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13610,7 +13626,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>v=DKIM1; p=</t>
+          <t>v=DMARC1; p=reject; sp=reject; adkim=s; aspf=s;</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -13640,12 +13656,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.509152Z</t>
+          <t>2021-12-12T16:20:23.516418Z</t>
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
@@ -13655,12 +13671,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>af815c727d2b5518ef3190a388afbce1</t>
+          <t>174e7c363d39762d0e764dca9d4f83fe</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>videodioggi.com</t>
+          <t>*._domainkey.videodioggi.com</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13670,7 +13686,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>v=spf1 -all</t>
+          <t>v=DKIM1; p=</t>
         </is>
       </c>
       <c r="E220" t="b">
@@ -13700,12 +13716,12 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2021-12-12T16:20:23.51106Z</t>
+          <t>2021-12-12T16:20:23.509152Z</t>
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
@@ -13715,29 +13731,29 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>cd8e879f3c9881e570af82269bcd0477</t>
+          <t>af815c727d2b5518ef3190a388afbce1</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
+          <t>videodioggi.com</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>185.199.108.153</t>
+          <t>v=spf1 -all</t>
         </is>
       </c>
       <c r="E221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
         <v>1</v>
@@ -13760,12 +13776,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:11.98058Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2023-03-30T09:59:12.228482Z</t>
+          <t>2021-12-12T16:20:23.51106Z</t>
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
@@ -13775,12 +13791,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>203ca5160347df21edeb2dcfafacdbf8</t>
+          <t>cd8e879f3c9881e570af82269bcd0477</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>test2.webtek.live</t>
+          <t>dasdsadsadasdasdasdasasas.webtek.live</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13820,12 +13836,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:29.902515Z</t>
+          <t>2023-03-30T09:59:11.98058Z</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2023-03-28T08:34:30.164318Z</t>
+          <t>2023-03-30T09:59:12.228482Z</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -13835,12 +13851,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>432df2553b443742f9f905e155878536</t>
+          <t>203ca5160347df21edeb2dcfafacdbf8</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>test.webtek.live</t>
+          <t>test2.webtek.live</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13880,12 +13896,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.078812Z</t>
+          <t>2023-03-28T08:34:29.902515Z</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2023-03-24T11:44:15.367412Z</t>
+          <t>2023-03-28T08:34:30.164318Z</t>
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
@@ -13895,12 +13911,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
+          <t>432df2553b443742f9f905e155878536</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>webtek.live</t>
+          <t>test.webtek.live</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13940,12 +13956,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.078812Z</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2023-02-17T23:14:39.792808Z</t>
+          <t>2023-03-24T11:44:15.367412Z</t>
         </is>
       </c>
       <c r="N224" t="inlineStr"/>
@@ -13955,22 +13971,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>add653a25af3cf87d882f89eb8c305c0</t>
+          <t>0f6431cd01ce8d23f5e6116a84799b6d</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>transversalpuntozero.org</t>
+          <t>webtek.live</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>transversalpuntozero.pages.dev</t>
+          <t>185.199.108.153</t>
         </is>
       </c>
       <c r="E225" t="b">
@@ -13984,7 +14000,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14000,17 +14016,77 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2024-11-03T08:47:11.475444Z</t>
+          <t>2023-02-17T23:14:39.792808Z</t>
         </is>
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>add653a25af3cf87d882f89eb8c305c0</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.org</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CNAME</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>transversalpuntozero.pages.dev</t>
+        </is>
+      </c>
+      <c r="E226" t="b">
+        <v>1</v>
+      </c>
+      <c r="F226" t="b">
+        <v>1</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>{'flatten_cname': False}</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2024-11-03T08:47:11.475444Z</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/cloudflare_dns_records.xlsx
+++ b/exports/cloudflare_dns_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P226"/>
+  <dimension ref="A1:P227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,12 +1553,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
+          <t>d173ba5139b4f9f794a65a183fd4a962</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>www.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>185.199.109.153</t>
+          <t>192.0.2.1</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1590,7 +1590,11 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Created during Cloudflare Rules deployment process for Redirect from root to WWW [Template]</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1598,44 +1602,48 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2025-07-01T16:44:05.723652Z</t>
+          <t>2026-05-16T07:34:19.256429Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-07-01T16:47:41.146282Z</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>2026-05-16T07:34:19.256429Z</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-05-16T07:34:19.256429Z</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9a0c1ea7682256e45af5f83341fb113e</t>
+          <t>8a036c1d5ddf43f61d7d48e78f41f72c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>www.certmate.org</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>185.199.109.153</t>
         </is>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1647,7 +1655,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1658,24 +1666,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:44:05.723652Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.571955Z</t>
+          <t>2025-07-01T16:47:41.146282Z</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>34</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aecf0cef3bc28aa58695c24be19d992c</t>
+          <t>9a0c1ea7682256e45af5f83341fb113e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1690,7 +1696,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>route2.mx.cloudflare.net</t>
+          <t>route3.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1720,24 +1726,24 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.566821Z</t>
+          <t>2025-07-01T21:19:12.571955Z</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fd67f08c9417a7d074fabd7e5513f715</t>
+          <t>aecf0cef3bc28aa58695c24be19d992c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1752,7 +1758,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>route1.mx.cloudflare.net</t>
+          <t>route2.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1782,39 +1788,39 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.555505Z</t>
+          <t>2025-07-01T21:19:12.566821Z</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14ecb7082a212233d816e345eea11668</t>
+          <t>fd67f08c9417a7d074fabd7e5513f715</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>test.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ns-858.awsdns-43.net</t>
+          <t>route1.mx.cloudflare.net</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1833,7 +1839,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1844,22 +1850,24 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01T21:29:05.514677Z</t>
+          <t>2025-07-01T21:19:12.555505Z</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0b4d1e1437d207800341e642f54e492f</t>
+          <t>14ecb7082a212233d816e345eea11668</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1874,7 +1882,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ns-8.awsdns-01.com</t>
+          <t>ns-858.awsdns-43.net</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1904,12 +1912,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:53.126097Z</t>
+          <t>2025-07-01T21:29:05.514677Z</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1919,7 +1927,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
+          <t>0b4d1e1437d207800341e642f54e492f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1934,7 +1942,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ns-1790.awsdns-31.co.uk</t>
+          <t>ns-8.awsdns-01.com</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1964,12 +1972,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:33.857419Z</t>
+          <t>2025-07-01T21:28:53.126097Z</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1979,7 +1987,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>759120960fb1797f3ceb20a074397a60</t>
+          <t>9c2a6ed018afd465d2a5ce93c4894ef1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ns-1479.awsdns-56.org</t>
+          <t>ns-1790.awsdns-31.co.uk</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -2024,12 +2032,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-07-01T21:28:13.948625Z</t>
+          <t>2025-07-01T21:28:33.857419Z</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2039,22 +2047,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>abd1e138555a9935af96e12e735ae62e</t>
+          <t>759120960fb1797f3ceb20a074397a60</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>certmate.org</t>
+          <t>test.certmate.org</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
+          <t>ns-1479.awsdns-56.org</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2084,12 +2092,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.576866Z</t>
+          <t>2025-07-01T21:28:13.948625Z</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2099,12 +2107,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
+          <t>abd1e138555a9935af96e12e735ae62e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cf2024-1._domainkey.certmate.org</t>
+          <t>certmate.org</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2114,7 +2122,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
+          <t>"v=spf1 include:_spf.mx.cloudflare.net ~all"</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2133,7 +2141,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -2144,12 +2152,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-07-01T21:19:12.582969Z</t>
+          <t>2025-07-01T21:19:12.576866Z</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2159,12 +2167,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a2f19ece8ecd17be41ef5df6ea93c77e</t>
+          <t>646969ffbd1d8c388fcb28dd08e4b889</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>_dmarc.certmate.org</t>
+          <t>cf2024-1._domainkey.certmate.org</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2174,7 +2182,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"v=DMARC1; p=none; rua=mailto:3f368183f1a544e1978df05d72916646@dmarc-reports.cloudflare.net"</t>
+          <t>"v=DKIM1; h=sha256; k=rsa; p=MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAiweykoi+o48IOGuP7GR3X0MOExCUDY/BCRHoWBnh3rChl7WhdyCxW3jgq1daEjPPqoi7sJvdg5hEQVsgVRQP4DcnQDVjGMbASQtrY4WmB1VebF+RPJB2ECPsEDTpeiI5ZyUAwJaVX7r6bznU67g7LvFq35yIo4sdlmtZGV+i0H4cpYH9+3JJ78k" "m4KXwaf9xUJCWF6nxeD+qG6Fyruw1Qlbds2r85U9dkNDVAS3gioCvELryh1TxKGiVTkg4wqHTyHfWsp7KD3WQHYJn0RyfJJu6YEmL77zonn7p2SRMvTMP3ZEXibnC9gz3nnhR6wcYL8Q7zXypKTMD58bTixDSJwIDAQAB"</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -2193,7 +2201,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'email_routing': True, 'read_only': True}</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -2204,12 +2212,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-05-04T08:08:44.893264Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-05-04T08:08:44.893264Z</t>
+          <t>2025-07-01T21:19:12.582969Z</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2219,36 +2227,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
+          <t>a2f19ece8ecd17be41ef5df6ea93c77e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>admin.cyberapi.io</t>
+          <t>_dmarc.certmate.org</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CNAME</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
+          <t>"v=DMARC1; p=none; rua=mailto:3f368183f1a544e1978df05d72916646@dmarc-reports.cloudflare.net"</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{'flatten_cname': False}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2264,12 +2272,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2025-12-14T18:45:26.130248Z</t>
+          <t>2026-05-04T08:08:44.893264Z</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2279,12 +2287,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>399a162cccc0c454242587f0c65bab6e</t>
+          <t>e3686ecfcca7678a06d3d56e3afeaf52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>docs.cyberapi.io</t>
+          <t>admin.cyberapi.io</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2294,14 +2302,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>b7c3a47d-f47d-40ce-92ce-5ca441f1f4da.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -2324,12 +2332,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2025-12-14T17:33:03.129276Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-12-14T18:01:58.535281Z</t>
+          <t>2025-12-14T18:45:26.130248Z</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2339,12 +2347,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>51c90000bf7340aba030440f7d7324e1</t>
+          <t>399a162cccc0c454242587f0c65bab6e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mt73.cyberapi.io</t>
+          <t>docs.cyberapi.io</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>smtp.mailtrap.live</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2384,12 +2392,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T17:33:03.129276Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:38.465176Z</t>
+          <t>2025-12-14T18:01:58.535281Z</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2399,12 +2407,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bdc3330689d167f9812b1263572a4ccb</t>
+          <t>51c90000bf7340aba030440f7d7324e1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mt-link.cyberapi.io</t>
+          <t>mt73.cyberapi.io</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2414,7 +2422,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>t.mailtrap.live</t>
+          <t>smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -2444,12 +2452,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:37.111487Z</t>
+          <t>2025-12-13T22:11:38.465176Z</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2459,12 +2467,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>e5fcf6b15716297a5d2186248ae9a854</t>
+          <t>bdc3330689d167f9812b1263572a4ccb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>poc.cyberapi.io</t>
+          <t>mt-link.cyberapi.io</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,14 +2482,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
+          <t>t.mailtrap.live</t>
         </is>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -2504,12 +2512,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T15:03:26.738652Z</t>
+          <t>2025-12-13T22:12:37.111487Z</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2519,12 +2527,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
+          <t>e5fcf6b15716297a5d2186248ae9a854</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>poc-t1.cyberapi.io</t>
+          <t>poc.cyberapi.io</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2564,12 +2572,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T18:46:50.475317Z</t>
+          <t>2026-03-24T15:03:26.738652Z</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2579,12 +2587,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
+          <t>bb75a13b8424957f2cd4a7f9164fd5fc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>poc-t2.cyberapi.io</t>
+          <t>poc-t1.cyberapi.io</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2624,12 +2632,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:03.486962Z</t>
+          <t>2026-03-24T18:46:50.475317Z</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2639,12 +2647,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>864de75a873870b7681170b09d376c13</t>
+          <t>8ab7f7eaa8373b1d744d670f479d2c84</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poc-t3.cyberapi.io</t>
+          <t>poc-t2.cyberapi.io</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2684,12 +2692,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:16.170381Z</t>
+          <t>2026-03-24T18:47:03.486962Z</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2699,12 +2707,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1b02a47cd362942d252c1b985894c35a</t>
+          <t>864de75a873870b7681170b09d376c13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poc-t4.cyberapi.io</t>
+          <t>poc-t3.cyberapi.io</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2744,12 +2752,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:28.310851Z</t>
+          <t>2026-03-24T18:47:16.170381Z</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2759,12 +2767,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>495419b8c428fd1f648d0429a17fbe1c</t>
+          <t>1b02a47cd362942d252c1b985894c35a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>poc-t5.cyberapi.io</t>
+          <t>poc-t4.cyberapi.io</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2804,12 +2812,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:40.134902Z</t>
+          <t>2026-03-24T18:47:28.310851Z</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2819,12 +2827,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c299e7513c4d25b2081f73236040cc69</t>
+          <t>495419b8c428fd1f648d0429a17fbe1c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>poc-t6.cyberapi.io</t>
+          <t>poc-t5.cyberapi.io</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2864,12 +2872,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T18:47:52.211476Z</t>
+          <t>2026-03-24T18:47:40.134902Z</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2879,12 +2887,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
+          <t>c299e7513c4d25b2081f73236040cc69</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>poc-t7.cyberapi.io</t>
+          <t>poc-t6.cyberapi.io</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2924,12 +2932,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:04.17506Z</t>
+          <t>2026-03-24T18:47:52.211476Z</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2939,12 +2947,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>86c96588cc20e61f4af5ebd8e1953428</t>
+          <t>e4b3c7c208e20ea21ab013bc9f77dbe2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>poc-t8.cyberapi.io</t>
+          <t>poc-t7.cyberapi.io</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2984,12 +2992,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T18:48:15.747165Z</t>
+          <t>2026-03-24T18:48:04.17506Z</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2999,12 +3007,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
+          <t>86c96588cc20e61f4af5ebd8e1953428</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>recaptcha.cyberapi.io</t>
+          <t>poc-t8.cyberapi.io</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3044,12 +3052,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T16:44:36.25606Z</t>
+          <t>2026-03-24T18:48:15.747165Z</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3059,12 +3067,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
+          <t>1f850c9b67a0858a6353fee6f9a9fd91</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rwmt1._domainkey.cyberapi.io</t>
+          <t>recaptcha.cyberapi.io</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3074,14 +3082,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rwmt1.dkim.smtp.mailtrap.live</t>
+          <t>9484c24d-3a2d-403a-80cd-9ec78cb0870c.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -3104,12 +3112,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-12-13T22:11:55.025852Z</t>
+          <t>2026-03-24T16:44:36.25606Z</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3119,12 +3127,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>52fdc262a215ba1f26603dc583c60d4f</t>
+          <t>ccd0fad434ee2c4e055b1a7cb0956b45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rwmt2._domainkey.cyberapi.io</t>
+          <t>rwmt1._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3134,7 +3142,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rwmt2.dkim.smtp.mailtrap.live</t>
+          <t>rwmt1.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3164,12 +3172,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-12-13T22:12:08.865348Z</t>
+          <t>2025-12-13T22:11:55.025852Z</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3179,12 +3187,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
+          <t>52fdc262a215ba1f26603dc583c60d4f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>threats.cyberapi.io</t>
+          <t>rwmt2._domainkey.cyberapi.io</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3194,14 +3202,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
+          <t>rwmt2.dkim.smtp.mailtrap.live</t>
         </is>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -3224,12 +3232,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:35.097237Z</t>
+          <t>2025-12-13T22:12:08.865348Z</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3239,12 +3247,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
+          <t>c2c1e12b0279dfa45e834f0d8037b56e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>turnstile.cyberapi.io</t>
+          <t>threats.cyberapi.io</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,7 +3262,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fabriziosalmi.github.io</t>
+          <t>55ceafb0-4a30-44ad-bacf-5eb5ad8bea7a.cfargotunnel.com</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -3284,12 +3292,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-03-20T23:15:01.418274Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T23:17:35.94124Z</t>
+          <t>2025-12-14T09:25:35.097237Z</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3299,12 +3307,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
+          <t>7c6a37903c87660f3d481dcaaf4c58a0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>www.cyberapi.io</t>
+          <t>turnstile.cyberapi.io</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3314,14 +3322,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cyberapi-io.github.io</t>
+          <t>fabriziosalmi.github.io</t>
         </is>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -3344,12 +3352,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2025-12-14T09:25:51.190941Z</t>
+          <t>2026-03-20T23:15:01.418274Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-12-14T18:31:58.065225Z</t>
+          <t>2026-03-20T23:17:35.94124Z</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3359,26 +3367,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
+          <t>29ccad680b767f5ed8fe5bd90e60f329</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cyberapi.io</t>
+          <t>www.cyberapi.io</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CNAME</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>route3.mx.cloudflare.net</t>
+          <t>cyberapi-io.github.io</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -3388,12 +3396,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{'flatten_cname': False}</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'email_routing': True, 'read_only': True}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3404,24 +3412,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T09:25:51.190941Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-12-13T22:19:39.326547Z</t>
+          <t>2025-12-14T18:31:58.065225Z</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>80</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3a04d418a0cd0940c289eb2ee57e8f05</t>
+          <t>b19c130de4a8b16f9ed4e6de341b1df4</t>
         </is>
       </c>
       <c r